--- a/Iteration 3/Risk-Register.xlsx
+++ b/Iteration 3/Risk-Register.xlsx
@@ -5,12 +5,12 @@
   <workbookPr autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sara\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://temahau-my.sharepoint.com/personal/scatta1_student_eit_ac_nz/Documents/Desktop/AgileProject/AgileProjects_Repository/Iteration 3/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A2F9314-DDDE-456B-86E7-E230A005C34E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="55" documentId="13_ncr:1_{8A2F9314-DDDE-456B-86E7-E230A005C34E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BB5B4AB0-45D7-46E4-9F4E-BC1C79CA81CE}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Example risk register" sheetId="8" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="107">
   <si>
     <t>REF ID</t>
   </si>
@@ -326,6 +326,78 @@
   <si>
     <t xml:space="preserve"> Syncing Git Repository Issues</t>
   </si>
+  <si>
+    <t xml:space="preserve">Miscomminication with goals for project </t>
+  </si>
+  <si>
+    <t>Commincation of the goals and deliverables</t>
+  </si>
+  <si>
+    <t xml:space="preserve">If communication isnt done effectively  </t>
+  </si>
+  <si>
+    <t>Formally plan future comminication in detail</t>
+  </si>
+  <si>
+    <t>No issues present/Under monitoring</t>
+  </si>
+  <si>
+    <t>unautherised access to project files and data</t>
+  </si>
+  <si>
+    <t>Members reciveing phising emails/messages</t>
+  </si>
+  <si>
+    <t>Members fall for phising emails/messages</t>
+  </si>
+  <si>
+    <t>No issues found/training project members</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Report and recover data and train members </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Full stack developer resigning </t>
+  </si>
+  <si>
+    <t>difficult development stages/any time</t>
+  </si>
+  <si>
+    <t>asinging big work loads to developer</t>
+  </si>
+  <si>
+    <t>hire a new developer/break up work laods</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No issues/ under monitoring </t>
+  </si>
+  <si>
+    <t>Project Manager</t>
+  </si>
+  <si>
+    <t>Legal councel, Project manager</t>
+  </si>
+  <si>
+    <t>Commincations manager, PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> scheduling isnt cleary defined for goals and deliverables</t>
+  </si>
+  <si>
+    <t>when scheduling a project or deliverable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">incorrect scheduling information </t>
+  </si>
+  <si>
+    <t>diagnose causes, adjust scheduling accordingly, stronger communication</t>
+  </si>
+  <si>
+    <t>Closly monitoring with no errors found</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Project monitoring </t>
+  </si>
 </sst>
 </file>
 
@@ -335,7 +407,7 @@
     <numFmt numFmtId="164" formatCode="mm/dd/yy;@"/>
     <numFmt numFmtId="165" formatCode="dd/mm/yy;@"/>
   </numFmts>
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -461,6 +533,18 @@
       <color theme="1"/>
       <name val="Century Gothic"/>
       <family val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Century Gothic"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="7.4"/>
+      <color theme="1"/>
+      <name val="Century Gothic"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="23">
@@ -692,7 +776,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="70">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1" indent="1"/>
@@ -881,11 +965,17 @@
     <xf numFmtId="0" fontId="2" fillId="22" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="165" fontId="2" fillId="16" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="16" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1746,26 +1836,26 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:IW27"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.33203125" customWidth="1"/>
-    <col min="2" max="2" width="10.83203125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="10.83203125" style="5" customWidth="1"/>
+    <col min="1" max="1" width="3.375" customWidth="1"/>
+    <col min="2" max="2" width="10.875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="10.875" style="5" customWidth="1"/>
     <col min="4" max="4" width="13.5" style="1" customWidth="1"/>
     <col min="5" max="5" width="20.5" style="1" customWidth="1"/>
-    <col min="6" max="6" width="12.83203125" style="5" customWidth="1"/>
-    <col min="7" max="7" width="12.83203125" style="1" customWidth="1"/>
-    <col min="8" max="8" width="13.83203125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="20.83203125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="15.83203125" style="1" customWidth="1"/>
-    <col min="11" max="11" width="25.83203125" style="1" customWidth="1"/>
-    <col min="12" max="12" width="15.83203125" style="1" customWidth="1"/>
-    <col min="13" max="13" width="12.83203125" style="1" customWidth="1"/>
-    <col min="14" max="14" width="20.83203125" style="1" customWidth="1"/>
-    <col min="15" max="15" width="3.33203125" customWidth="1"/>
+    <col min="6" max="6" width="12.875" style="5" customWidth="1"/>
+    <col min="7" max="7" width="12.875" style="1" customWidth="1"/>
+    <col min="8" max="8" width="13.875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="20.875" style="1" customWidth="1"/>
+    <col min="10" max="10" width="15.875" style="1" customWidth="1"/>
+    <col min="11" max="11" width="25.875" style="1" customWidth="1"/>
+    <col min="12" max="12" width="15.875" style="1" customWidth="1"/>
+    <col min="13" max="13" width="12.875" style="1" customWidth="1"/>
+    <col min="14" max="14" width="20.875" style="1" customWidth="1"/>
+    <col min="15" max="15" width="3.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:257" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:257" x14ac:dyDescent="0.25">
       <c r="B1"/>
       <c r="C1"/>
       <c r="D1"/>
@@ -1780,7 +1870,7 @@
       <c r="M1"/>
       <c r="N1"/>
     </row>
-    <row r="2" spans="1:257" s="46" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:257" s="46" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="47"/>
       <c r="B2" s="48" t="s">
         <v>76</v>
@@ -2041,7 +2131,7 @@
       <c r="IV2" s="47"/>
       <c r="IW2" s="47"/>
     </row>
-    <row r="3" spans="1:257" ht="139" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:257" ht="138.94999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C3" s="1"/>
       <c r="F3" s="1"/>
       <c r="K3"/>
@@ -2049,13 +2139,13 @@
       <c r="M3"/>
       <c r="N3"/>
     </row>
-    <row r="4" spans="1:257" ht="79" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:257" ht="78.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B4" s="63"/>
       <c r="C4"/>
-      <c r="D4" s="66" t="s">
+      <c r="D4" s="67" t="s">
         <v>45</v>
       </c>
-      <c r="E4" s="66"/>
+      <c r="E4" s="67"/>
       <c r="F4"/>
       <c r="G4"/>
       <c r="H4" s="62" t="s">
@@ -2068,7 +2158,7 @@
       <c r="M4"/>
       <c r="N4"/>
     </row>
-    <row r="5" spans="1:257" s="4" customFormat="1" ht="55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:257" s="4" customFormat="1" ht="54.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="3"/>
       <c r="B5" s="49" t="s">
         <v>0</v>
@@ -2111,7 +2201,7 @@
       </c>
       <c r="O5" s="3"/>
     </row>
-    <row r="6" spans="1:257" ht="100" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:257" ht="108" x14ac:dyDescent="0.25">
       <c r="B6" s="53">
         <v>10001</v>
       </c>
@@ -2151,7 +2241,7 @@
       </c>
       <c r="N6" s="65"/>
     </row>
-    <row r="7" spans="1:257" ht="100" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:257" ht="121.5" x14ac:dyDescent="0.25">
       <c r="B7" s="55">
         <v>10002</v>
       </c>
@@ -2191,7 +2281,7 @@
       </c>
       <c r="N7" s="65"/>
     </row>
-    <row r="8" spans="1:257" ht="100" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:257" ht="108" x14ac:dyDescent="0.25">
       <c r="B8" s="55">
         <v>10003</v>
       </c>
@@ -2231,7 +2321,7 @@
       </c>
       <c r="N8" s="65"/>
     </row>
-    <row r="9" spans="1:257" ht="75" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:257" ht="81" x14ac:dyDescent="0.25">
       <c r="B9" s="55">
         <v>10004</v>
       </c>
@@ -2271,7 +2361,7 @@
       </c>
       <c r="N9" s="65"/>
     </row>
-    <row r="10" spans="1:257" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:257" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="55"/>
       <c r="C10" s="54"/>
       <c r="D10" s="39"/>
@@ -2293,7 +2383,7 @@
       <c r="M10" s="64"/>
       <c r="N10" s="65"/>
     </row>
-    <row r="11" spans="1:257" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:257" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="55"/>
       <c r="C11" s="54"/>
       <c r="D11" s="39"/>
@@ -2315,7 +2405,7 @@
       <c r="M11" s="64"/>
       <c r="N11" s="65"/>
     </row>
-    <row r="12" spans="1:257" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:257" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="55"/>
       <c r="C12" s="54"/>
       <c r="D12" s="39"/>
@@ -2337,7 +2427,7 @@
       <c r="M12" s="64"/>
       <c r="N12" s="65"/>
     </row>
-    <row r="13" spans="1:257" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:257" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="55"/>
       <c r="C13" s="54"/>
       <c r="D13" s="39"/>
@@ -2359,7 +2449,7 @@
       <c r="M13" s="64"/>
       <c r="N13" s="65"/>
     </row>
-    <row r="14" spans="1:257" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:257" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="55"/>
       <c r="C14" s="54"/>
       <c r="D14" s="39"/>
@@ -2381,7 +2471,7 @@
       <c r="M14" s="64"/>
       <c r="N14" s="65"/>
     </row>
-    <row r="15" spans="1:257" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:257" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="55"/>
       <c r="C15" s="54"/>
       <c r="D15" s="39"/>
@@ -2403,7 +2493,7 @@
       <c r="M15" s="64"/>
       <c r="N15" s="65"/>
     </row>
-    <row r="16" spans="1:257" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:257" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="55"/>
       <c r="C16" s="54"/>
       <c r="D16" s="39"/>
@@ -2425,7 +2515,7 @@
       <c r="M16" s="64"/>
       <c r="N16" s="65"/>
     </row>
-    <row r="17" spans="2:14" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:14" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="55"/>
       <c r="C17" s="54"/>
       <c r="D17" s="39"/>
@@ -2447,7 +2537,7 @@
       <c r="M17" s="64"/>
       <c r="N17" s="65"/>
     </row>
-    <row r="18" spans="2:14" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:14" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="55"/>
       <c r="C18" s="54"/>
       <c r="D18" s="39"/>
@@ -2469,15 +2559,15 @@
       <c r="M18" s="64"/>
       <c r="N18" s="65"/>
     </row>
-    <row r="19" spans="2:14" ht="18" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="20" spans="2:14" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="21" spans="2:14" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="22" spans="2:14" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="23" spans="2:14" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="24" spans="2:14" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="25" spans="2:14" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="26" spans="2:14" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="27" spans="2:14" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="19" spans="2:14" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="20" spans="2:14" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="21" spans="2:14" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="22" spans="2:14" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="23" spans="2:14" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="24" spans="2:14" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="25" spans="2:14" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="26" spans="2:14" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="27" spans="2:14" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="D4:E4"/>
@@ -2575,23 +2665,23 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:IW43"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.33203125" customWidth="1"/>
-    <col min="2" max="2" width="10.83203125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="10.83203125" style="5" customWidth="1"/>
+    <col min="1" max="1" width="3.375" customWidth="1"/>
+    <col min="2" max="2" width="10.875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="10.875" style="5" customWidth="1"/>
     <col min="4" max="4" width="13.5" style="1" customWidth="1"/>
-    <col min="5" max="5" width="29.33203125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="12.83203125" style="5" customWidth="1"/>
-    <col min="7" max="7" width="12.83203125" style="1" customWidth="1"/>
-    <col min="8" max="8" width="13.83203125" style="1" customWidth="1"/>
-    <col min="9" max="12" width="15.83203125" style="1" customWidth="1"/>
-    <col min="13" max="13" width="12.83203125" style="1" customWidth="1"/>
-    <col min="14" max="14" width="20.83203125" style="1" customWidth="1"/>
-    <col min="15" max="15" width="3.33203125" customWidth="1"/>
+    <col min="5" max="5" width="29.375" style="1" customWidth="1"/>
+    <col min="6" max="6" width="12.875" style="5" customWidth="1"/>
+    <col min="7" max="7" width="12.875" style="1" customWidth="1"/>
+    <col min="8" max="8" width="13.875" style="1" customWidth="1"/>
+    <col min="9" max="12" width="15.875" style="1" customWidth="1"/>
+    <col min="13" max="13" width="12.875" style="1" customWidth="1"/>
+    <col min="14" max="14" width="20.875" style="1" customWidth="1"/>
+    <col min="15" max="15" width="3.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:257" s="46" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:257" s="46" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="47"/>
       <c r="B1" s="48" t="s">
         <v>77</v>
@@ -2852,7 +2942,7 @@
       <c r="IV1" s="47"/>
       <c r="IW1" s="47"/>
     </row>
-    <row r="2" spans="1:257" ht="139" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:257" ht="138.94999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C2" s="1"/>
       <c r="F2" s="1"/>
       <c r="K2"/>
@@ -2860,13 +2950,13 @@
       <c r="M2"/>
       <c r="N2"/>
     </row>
-    <row r="3" spans="1:257" ht="79" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:257" ht="78.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="63"/>
       <c r="C3"/>
-      <c r="D3" s="66" t="s">
+      <c r="D3" s="67" t="s">
         <v>45</v>
       </c>
-      <c r="E3" s="66"/>
+      <c r="E3" s="67"/>
       <c r="F3"/>
       <c r="G3"/>
       <c r="H3" s="62" t="s">
@@ -2879,7 +2969,7 @@
       <c r="M3"/>
       <c r="N3"/>
     </row>
-    <row r="4" spans="1:257" s="4" customFormat="1" ht="55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:257" s="4" customFormat="1" ht="54.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="3"/>
       <c r="B4" s="49" t="s">
         <v>0</v>
@@ -2922,11 +3012,11 @@
       </c>
       <c r="O4" s="3"/>
     </row>
-    <row r="5" spans="1:257" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:257" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="53">
         <v>1</v>
       </c>
-      <c r="C5" s="67">
+      <c r="C5" s="66">
         <v>46154</v>
       </c>
       <c r="D5" s="39"/>
@@ -2956,7 +3046,7 @@
       </c>
       <c r="N5" s="59"/>
     </row>
-    <row r="6" spans="1:257" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:257" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="55"/>
       <c r="C6" s="54"/>
       <c r="D6" s="39"/>
@@ -2978,79 +3068,153 @@
       <c r="M6" s="6"/>
       <c r="N6" s="59"/>
     </row>
-    <row r="7" spans="1:257" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B7" s="55"/>
-      <c r="C7" s="54"/>
+    <row r="7" spans="1:257" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="55">
+        <v>3</v>
+      </c>
+      <c r="C7" s="54">
+        <v>46155</v>
+      </c>
       <c r="D7" s="39"/>
-      <c r="E7" s="61"/>
-      <c r="F7" s="56"/>
-      <c r="G7" s="57"/>
+      <c r="E7" s="61" t="s">
+        <v>83</v>
+      </c>
+      <c r="F7" s="56">
+        <v>2</v>
+      </c>
+      <c r="G7" s="57">
+        <v>8</v>
+      </c>
       <c r="H7" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I7" s="61"/>
-      <c r="J7" s="61"/>
-      <c r="K7" s="61"/>
-      <c r="L7" s="61"/>
-      <c r="M7" s="6"/>
+        <v>16</v>
+      </c>
+      <c r="I7" s="61" t="s">
+        <v>84</v>
+      </c>
+      <c r="J7" s="61" t="s">
+        <v>85</v>
+      </c>
+      <c r="K7" s="61" t="s">
+        <v>86</v>
+      </c>
+      <c r="L7" s="61" t="s">
+        <v>87</v>
+      </c>
+      <c r="M7" s="6" t="s">
+        <v>100</v>
+      </c>
       <c r="N7" s="59"/>
     </row>
-    <row r="8" spans="1:257" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B8" s="55"/>
+    <row r="8" spans="1:257" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="55">
+        <v>4</v>
+      </c>
       <c r="C8" s="54"/>
       <c r="D8" s="39"/>
-      <c r="E8" s="61"/>
-      <c r="F8" s="56"/>
-      <c r="G8" s="57"/>
+      <c r="E8" s="61" t="s">
+        <v>88</v>
+      </c>
+      <c r="F8" s="56">
+        <v>5</v>
+      </c>
+      <c r="G8" s="57">
+        <v>16</v>
+      </c>
       <c r="H8" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I8" s="61"/>
-      <c r="J8" s="61"/>
-      <c r="K8" s="61"/>
-      <c r="L8" s="61"/>
-      <c r="M8" s="6"/>
+        <v>80</v>
+      </c>
+      <c r="I8" s="61" t="s">
+        <v>89</v>
+      </c>
+      <c r="J8" s="61" t="s">
+        <v>90</v>
+      </c>
+      <c r="K8" s="68" t="s">
+        <v>92</v>
+      </c>
+      <c r="L8" s="61" t="s">
+        <v>91</v>
+      </c>
+      <c r="M8" s="6" t="s">
+        <v>99</v>
+      </c>
       <c r="N8" s="59"/>
     </row>
-    <row r="9" spans="1:257" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B9" s="55"/>
+    <row r="9" spans="1:257" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="55">
+        <v>5</v>
+      </c>
       <c r="C9" s="54"/>
       <c r="D9" s="39"/>
-      <c r="E9" s="61"/>
-      <c r="F9" s="56"/>
-      <c r="G9" s="57"/>
+      <c r="E9" s="61" t="s">
+        <v>93</v>
+      </c>
+      <c r="F9" s="56">
+        <v>2</v>
+      </c>
+      <c r="G9" s="57">
+        <v>8</v>
+      </c>
       <c r="H9" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I9" s="61"/>
-      <c r="J9" s="61"/>
-      <c r="K9" s="61"/>
-      <c r="L9" s="61"/>
-      <c r="M9" s="6"/>
+        <v>16</v>
+      </c>
+      <c r="I9" s="61" t="s">
+        <v>94</v>
+      </c>
+      <c r="J9" s="61" t="s">
+        <v>95</v>
+      </c>
+      <c r="K9" s="61" t="s">
+        <v>96</v>
+      </c>
+      <c r="L9" s="61" t="s">
+        <v>97</v>
+      </c>
+      <c r="M9" s="6" t="s">
+        <v>98</v>
+      </c>
       <c r="N9" s="59"/>
     </row>
-    <row r="10" spans="1:257" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B10" s="55"/>
+    <row r="10" spans="1:257" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="55">
+        <v>6</v>
+      </c>
       <c r="C10" s="54"/>
       <c r="D10" s="39"/>
-      <c r="E10" s="61"/>
-      <c r="F10" s="56"/>
-      <c r="G10" s="57"/>
+      <c r="E10" s="61" t="s">
+        <v>101</v>
+      </c>
+      <c r="F10" s="56">
+        <v>3</v>
+      </c>
+      <c r="G10" s="57">
+        <v>16</v>
+      </c>
       <c r="H10" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I10" s="61"/>
-      <c r="J10" s="61"/>
-      <c r="K10" s="61"/>
-      <c r="L10" s="61"/>
-      <c r="M10" s="6"/>
+        <v>48</v>
+      </c>
+      <c r="I10" s="61" t="s">
+        <v>102</v>
+      </c>
+      <c r="J10" s="61" t="s">
+        <v>103</v>
+      </c>
+      <c r="K10" s="69" t="s">
+        <v>104</v>
+      </c>
+      <c r="L10" s="61" t="s">
+        <v>105</v>
+      </c>
+      <c r="M10" s="6" t="s">
+        <v>106</v>
+      </c>
       <c r="N10" s="59"/>
     </row>
-    <row r="11" spans="1:257" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:257" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="55"/>
       <c r="C11" s="54"/>
       <c r="D11" s="39"/>
@@ -3068,7 +3232,7 @@
       <c r="M11" s="6"/>
       <c r="N11" s="59"/>
     </row>
-    <row r="12" spans="1:257" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:257" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="55"/>
       <c r="C12" s="54"/>
       <c r="D12" s="39"/>
@@ -3086,7 +3250,7 @@
       <c r="M12" s="6"/>
       <c r="N12" s="59"/>
     </row>
-    <row r="13" spans="1:257" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:257" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="55"/>
       <c r="C13" s="54"/>
       <c r="D13" s="39"/>
@@ -3104,7 +3268,7 @@
       <c r="M13" s="6"/>
       <c r="N13" s="59"/>
     </row>
-    <row r="14" spans="1:257" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:257" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="55"/>
       <c r="C14" s="54"/>
       <c r="D14" s="39"/>
@@ -3122,7 +3286,7 @@
       <c r="M14" s="6"/>
       <c r="N14" s="59"/>
     </row>
-    <row r="15" spans="1:257" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:257" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="55"/>
       <c r="C15" s="54"/>
       <c r="D15" s="39"/>
@@ -3140,7 +3304,7 @@
       <c r="M15" s="6"/>
       <c r="N15" s="59"/>
     </row>
-    <row r="16" spans="1:257" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:257" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="55"/>
       <c r="C16" s="54"/>
       <c r="D16" s="39"/>
@@ -3158,7 +3322,7 @@
       <c r="M16" s="6"/>
       <c r="N16" s="59"/>
     </row>
-    <row r="17" spans="2:14" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:14" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="55"/>
       <c r="C17" s="54"/>
       <c r="D17" s="39"/>
@@ -3176,7 +3340,7 @@
       <c r="M17" s="6"/>
       <c r="N17" s="59"/>
     </row>
-    <row r="18" spans="2:14" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:14" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="55"/>
       <c r="C18" s="54"/>
       <c r="D18" s="39"/>
@@ -3194,7 +3358,7 @@
       <c r="M18" s="6"/>
       <c r="N18" s="59"/>
     </row>
-    <row r="19" spans="2:14" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:14" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" s="55"/>
       <c r="C19" s="54"/>
       <c r="D19" s="39"/>
@@ -3212,7 +3376,7 @@
       <c r="M19" s="6"/>
       <c r="N19" s="59"/>
     </row>
-    <row r="20" spans="2:14" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:14" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="55"/>
       <c r="C20" s="54"/>
       <c r="D20" s="39"/>
@@ -3230,7 +3394,7 @@
       <c r="M20" s="6"/>
       <c r="N20" s="59"/>
     </row>
-    <row r="21" spans="2:14" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:14" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B21" s="55"/>
       <c r="C21" s="54"/>
       <c r="D21" s="39"/>
@@ -3248,7 +3412,7 @@
       <c r="M21" s="6"/>
       <c r="N21" s="59"/>
     </row>
-    <row r="22" spans="2:14" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:14" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="55"/>
       <c r="C22" s="54"/>
       <c r="D22" s="39"/>
@@ -3266,7 +3430,7 @@
       <c r="M22" s="6"/>
       <c r="N22" s="59"/>
     </row>
-    <row r="23" spans="2:14" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:14" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B23" s="55"/>
       <c r="C23" s="54"/>
       <c r="D23" s="39"/>
@@ -3284,7 +3448,7 @@
       <c r="M23" s="6"/>
       <c r="N23" s="59"/>
     </row>
-    <row r="24" spans="2:14" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:14" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24" s="55"/>
       <c r="C24" s="54"/>
       <c r="D24" s="39"/>
@@ -3302,7 +3466,7 @@
       <c r="M24" s="6"/>
       <c r="N24" s="59"/>
     </row>
-    <row r="25" spans="2:14" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:14" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B25" s="55"/>
       <c r="C25" s="54"/>
       <c r="D25" s="39"/>
@@ -3320,7 +3484,7 @@
       <c r="M25" s="6"/>
       <c r="N25" s="59"/>
     </row>
-    <row r="26" spans="2:14" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:14" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="55"/>
       <c r="C26" s="54"/>
       <c r="D26" s="39"/>
@@ -3338,7 +3502,7 @@
       <c r="M26" s="6"/>
       <c r="N26" s="59"/>
     </row>
-    <row r="27" spans="2:14" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:14" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B27" s="55"/>
       <c r="C27" s="54"/>
       <c r="D27" s="39"/>
@@ -3356,7 +3520,7 @@
       <c r="M27" s="6"/>
       <c r="N27" s="59"/>
     </row>
-    <row r="28" spans="2:14" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:14" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B28" s="55"/>
       <c r="C28" s="54"/>
       <c r="D28" s="39"/>
@@ -3374,7 +3538,7 @@
       <c r="M28" s="6"/>
       <c r="N28" s="59"/>
     </row>
-    <row r="29" spans="2:14" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:14" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B29" s="55"/>
       <c r="C29" s="54"/>
       <c r="D29" s="39"/>
@@ -3392,7 +3556,7 @@
       <c r="M29" s="6"/>
       <c r="N29" s="59"/>
     </row>
-    <row r="30" spans="2:14" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:14" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B30" s="55"/>
       <c r="C30" s="54"/>
       <c r="D30" s="39"/>
@@ -3410,7 +3574,7 @@
       <c r="M30" s="6"/>
       <c r="N30" s="59"/>
     </row>
-    <row r="31" spans="2:14" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:14" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B31" s="55"/>
       <c r="C31" s="54"/>
       <c r="D31" s="39"/>
@@ -3428,7 +3592,7 @@
       <c r="M31" s="6"/>
       <c r="N31" s="59"/>
     </row>
-    <row r="32" spans="2:14" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:14" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B32" s="55"/>
       <c r="C32" s="54"/>
       <c r="D32" s="39"/>
@@ -3446,7 +3610,7 @@
       <c r="M32" s="6"/>
       <c r="N32" s="59"/>
     </row>
-    <row r="33" spans="2:14" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:14" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B33" s="55"/>
       <c r="C33" s="54"/>
       <c r="D33" s="39"/>
@@ -3464,7 +3628,7 @@
       <c r="M33" s="6"/>
       <c r="N33" s="59"/>
     </row>
-    <row r="34" spans="2:14" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:14" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B34" s="55"/>
       <c r="C34" s="54"/>
       <c r="D34" s="39"/>
@@ -3482,15 +3646,15 @@
       <c r="M34" s="6"/>
       <c r="N34" s="59"/>
     </row>
-    <row r="35" spans="2:14" ht="18" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="36" spans="2:14" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="37" spans="2:14" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="38" spans="2:14" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="39" spans="2:14" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="40" spans="2:14" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="41" spans="2:14" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="42" spans="2:14" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="43" spans="2:14" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="35" spans="2:14" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="36" spans="2:14" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="37" spans="2:14" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="38" spans="2:14" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="39" spans="2:14" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="40" spans="2:14" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="41" spans="2:14" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="42" spans="2:14" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="43" spans="2:14" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="D3:E3"/>
@@ -3587,21 +3751,21 @@
     <tabColor theme="2" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:IX27"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.33203125" customWidth="1"/>
-    <col min="2" max="4" width="22.83203125" customWidth="1"/>
-    <col min="5" max="5" width="3.33203125" customWidth="1"/>
+    <col min="1" max="1" width="3.375" customWidth="1"/>
+    <col min="2" max="4" width="22.875" customWidth="1"/>
+    <col min="5" max="5" width="3.375" customWidth="1"/>
     <col min="6" max="6" width="4" customWidth="1"/>
-    <col min="7" max="7" width="3.33203125" customWidth="1"/>
+    <col min="7" max="7" width="3.375" customWidth="1"/>
     <col min="13" max="13" width="6.5" customWidth="1"/>
-    <col min="14" max="14" width="19.83203125" customWidth="1"/>
-    <col min="15" max="15" width="3.33203125" customWidth="1"/>
-    <col min="16" max="16" width="19.83203125" customWidth="1"/>
-    <col min="17" max="17" width="3.33203125" customWidth="1"/>
+    <col min="14" max="14" width="19.875" customWidth="1"/>
+    <col min="15" max="15" width="3.375" customWidth="1"/>
+    <col min="16" max="16" width="19.875" customWidth="1"/>
+    <col min="17" max="17" width="3.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:258" s="46" customFormat="1" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:258" s="46" customFormat="1" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="47"/>
       <c r="B1" s="48" t="s">
         <v>27</v>
@@ -3863,7 +4027,7 @@
       <c r="IW1" s="47"/>
       <c r="IX1" s="47"/>
     </row>
-    <row r="2" spans="1:258" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:258" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="45" t="s">
         <v>26</v>
       </c>
@@ -3893,7 +4057,7 @@
       <c r="M2" s="43"/>
       <c r="O2" s="42"/>
     </row>
-    <row r="3" spans="1:258" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:258" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="40" t="s">
         <v>21</v>
       </c>
@@ -3930,7 +4094,7 @@
       <c r="M3" s="2"/>
       <c r="O3" s="19"/>
     </row>
-    <row r="4" spans="1:258" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:258" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="35" t="s">
         <v>18</v>
       </c>
@@ -3967,7 +4131,7 @@
       <c r="M4" s="2"/>
       <c r="O4" s="19"/>
     </row>
-    <row r="5" spans="1:258" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:258" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="29" t="s">
         <v>15</v>
       </c>
@@ -4004,7 +4168,7 @@
       <c r="M5" s="2"/>
       <c r="O5" s="19"/>
     </row>
-    <row r="6" spans="1:258" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:258" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="24" t="s">
         <v>12</v>
       </c>
@@ -4041,7 +4205,7 @@
       <c r="M6" s="2"/>
       <c r="O6" s="19"/>
     </row>
-    <row r="7" spans="1:258" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:258" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="17" t="s">
         <v>9</v>
       </c>
@@ -4076,7 +4240,7 @@
       </c>
       <c r="O7" s="10"/>
     </row>
-    <row r="8" spans="1:258" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:258" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="G8" s="8"/>
       <c r="H8" s="8"/>
       <c r="I8" s="8"/>
@@ -4084,7 +4248,7 @@
       <c r="K8" s="8"/>
       <c r="L8" s="8"/>
     </row>
-    <row r="9" spans="1:258" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:258" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="41" t="s">
         <v>23</v>
       </c>
@@ -4092,7 +4256,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="10" spans="1:258" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:258" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="37">
         <v>1</v>
       </c>
@@ -4100,7 +4264,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:258" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:258" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="31">
         <v>2</v>
       </c>
@@ -4108,7 +4272,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:258" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:258" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="26">
         <v>3</v>
       </c>
@@ -4116,7 +4280,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:258" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:258" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="20">
         <v>4</v>
       </c>
@@ -4124,7 +4288,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="14" spans="1:258" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:258" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="11">
         <v>5</v>
       </c>
@@ -4132,62 +4296,62 @@
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:258" ht="44.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:258" ht="44.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B16" s="63" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="17" spans="2:2" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="45" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="2:2" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="60" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="19" spans="2:2" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" s="60" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="20" spans="2:2" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="60" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="21" spans="2:2" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B21" s="60" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="22" spans="2:2" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="60" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="23" spans="2:2" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B23" s="60" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="24" spans="2:2" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24" s="60" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="25" spans="2:2" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B25" s="60" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="26" spans="2:2" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="60" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="27" spans="2:2" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B27" s="60" t="s">
         <v>43</v>
       </c>

--- a/Iteration 3/Risk-Register.xlsx
+++ b/Iteration 3/Risk-Register.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://temahau-my.sharepoint.com/personal/scatta1_student_eit_ac_nz/Documents/Desktop/AgileProject/AgileProjects_Repository/Iteration 3/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="55" documentId="13_ncr:1_{8A2F9314-DDDE-456B-86E7-E230A005C34E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BB5B4AB0-45D7-46E4-9F4E-BC1C79CA81CE}"/>
+  <xr:revisionPtr revIDLastSave="59" documentId="13_ncr:1_{8A2F9314-DDDE-456B-86E7-E230A005C34E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{34D8C1D5-0ED9-4C7B-9CD7-C0FFD1AD2411}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="107">
   <si>
     <t>REF ID</t>
   </si>
@@ -333,9 +333,6 @@
     <t>Commincation of the goals and deliverables</t>
   </si>
   <si>
-    <t xml:space="preserve">If communication isnt done effectively  </t>
-  </si>
-  <si>
     <t>Formally plan future comminication in detail</t>
   </si>
   <si>
@@ -381,9 +378,6 @@
     <t>Commincations manager, PM</t>
   </si>
   <si>
-    <t xml:space="preserve"> scheduling isnt cleary defined for goals and deliverables</t>
-  </si>
-  <si>
     <t>when scheduling a project or deliverable</t>
   </si>
   <si>
@@ -397,6 +391,12 @@
   </si>
   <si>
     <t xml:space="preserve">Project monitoring </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> scheduling isn't cleary defined for goals and deliverables</t>
+  </si>
+  <si>
+    <t xml:space="preserve">If communication isn't done effectively  </t>
   </si>
 </sst>
 </file>
@@ -968,14 +968,14 @@
     <xf numFmtId="165" fontId="2" fillId="16" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2142,10 +2142,10 @@
     <row r="4" spans="1:257" ht="78.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B4" s="63"/>
       <c r="C4"/>
-      <c r="D4" s="67" t="s">
+      <c r="D4" s="69" t="s">
         <v>45</v>
       </c>
-      <c r="E4" s="67"/>
+      <c r="E4" s="69"/>
       <c r="F4"/>
       <c r="G4"/>
       <c r="H4" s="62" t="s">
@@ -2953,10 +2953,10 @@
     <row r="3" spans="1:257" ht="78.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="63"/>
       <c r="C3"/>
-      <c r="D3" s="67" t="s">
+      <c r="D3" s="69" t="s">
         <v>45</v>
       </c>
-      <c r="E3" s="67"/>
+      <c r="E3" s="69"/>
       <c r="F3"/>
       <c r="G3"/>
       <c r="H3" s="62" t="s">
@@ -3093,16 +3093,16 @@
         <v>84</v>
       </c>
       <c r="J7" s="61" t="s">
+        <v>106</v>
+      </c>
+      <c r="K7" s="61" t="s">
         <v>85</v>
       </c>
-      <c r="K7" s="61" t="s">
+      <c r="L7" s="61" t="s">
         <v>86</v>
       </c>
-      <c r="L7" s="61" t="s">
-        <v>87</v>
-      </c>
       <c r="M7" s="6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="N7" s="59"/>
     </row>
@@ -3113,7 +3113,7 @@
       <c r="C8" s="54"/>
       <c r="D8" s="39"/>
       <c r="E8" s="61" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F8" s="56">
         <v>5</v>
@@ -3126,19 +3126,19 @@
         <v>80</v>
       </c>
       <c r="I8" s="61" t="s">
+        <v>88</v>
+      </c>
+      <c r="J8" s="61" t="s">
         <v>89</v>
       </c>
-      <c r="J8" s="61" t="s">
+      <c r="K8" s="67" t="s">
+        <v>91</v>
+      </c>
+      <c r="L8" s="61" t="s">
         <v>90</v>
       </c>
-      <c r="K8" s="68" t="s">
-        <v>92</v>
-      </c>
-      <c r="L8" s="61" t="s">
-        <v>91</v>
-      </c>
       <c r="M8" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="N8" s="59"/>
     </row>
@@ -3149,7 +3149,7 @@
       <c r="C9" s="54"/>
       <c r="D9" s="39"/>
       <c r="E9" s="61" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F9" s="56">
         <v>2</v>
@@ -3162,19 +3162,19 @@
         <v>16</v>
       </c>
       <c r="I9" s="61" t="s">
+        <v>93</v>
+      </c>
+      <c r="J9" s="61" t="s">
         <v>94</v>
       </c>
-      <c r="J9" s="61" t="s">
+      <c r="K9" s="61" t="s">
         <v>95</v>
       </c>
-      <c r="K9" s="61" t="s">
+      <c r="L9" s="61" t="s">
         <v>96</v>
       </c>
-      <c r="L9" s="61" t="s">
+      <c r="M9" s="6" t="s">
         <v>97</v>
-      </c>
-      <c r="M9" s="6" t="s">
-        <v>98</v>
       </c>
       <c r="N9" s="59"/>
     </row>
@@ -3185,7 +3185,7 @@
       <c r="C10" s="54"/>
       <c r="D10" s="39"/>
       <c r="E10" s="61" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="F10" s="56">
         <v>3</v>
@@ -3198,19 +3198,19 @@
         <v>48</v>
       </c>
       <c r="I10" s="61" t="s">
+        <v>100</v>
+      </c>
+      <c r="J10" s="61" t="s">
+        <v>101</v>
+      </c>
+      <c r="K10" s="68" t="s">
         <v>102</v>
       </c>
-      <c r="J10" s="61" t="s">
+      <c r="L10" s="61" t="s">
         <v>103</v>
       </c>
-      <c r="K10" s="69" t="s">
+      <c r="M10" s="6" t="s">
         <v>104</v>
-      </c>
-      <c r="L10" s="61" t="s">
-        <v>105</v>
-      </c>
-      <c r="M10" s="6" t="s">
-        <v>106</v>
       </c>
       <c r="N10" s="59"/>
     </row>

--- a/Iteration 3/Risk-Register.xlsx
+++ b/Iteration 3/Risk-Register.xlsx
@@ -5,12 +5,12 @@
   <workbookPr autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://temahau-my.sharepoint.com/personal/scatta1_student_eit_ac_nz/Documents/Desktop/AgileProject/AgileProjects_Repository/Iteration 3/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://temahau-my.sharepoint.com/personal/sellws2_student_eit_ac_nz/Documents/Documents/ITPM5.240 Agile Projects/Assignments/AgileProjects_Repository/Iteration 3/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="59" documentId="13_ncr:1_{8A2F9314-DDDE-456B-86E7-E230A005C34E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{34D8C1D5-0ED9-4C7B-9CD7-C0FFD1AD2411}"/>
+  <xr:revisionPtr revIDLastSave="116" documentId="13_ncr:1_{8A2F9314-DDDE-456B-86E7-E230A005C34E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BF9CD29A-52B2-4EBA-8999-6AA8AB4D59CB}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Example risk register" sheetId="8" r:id="rId1"/>
@@ -21,12 +21,12 @@
     <externalReference r:id="rId4"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'BLANK - Risk Reg'!$B$4:$N$34</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'BLANK - Risk Reg'!$B$4:$N$36</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Example risk register'!$B$5:$N$18</definedName>
     <definedName name="Type" localSheetId="2">'[1]Maintenance Work Order'!#REF!</definedName>
     <definedName name="Type">'[1]Maintenance Work Order'!#REF!</definedName>
   </definedNames>
-  <calcPr calcId="191029" concurrentCalc="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="117">
   <si>
     <t>REF ID</t>
   </si>
@@ -312,21 +312,9 @@
     <t>PROJECT RISK REGISTER TEMPALTE</t>
   </si>
   <si>
-    <t>Scope creep</t>
-  </si>
-  <si>
     <t>Project Manager, All Members</t>
   </si>
   <si>
-    <t>Risk can arise at any iteration of the project</t>
-  </si>
-  <si>
-    <t>If changes are made to the plan - ex</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Syncing Git Repository Issues</t>
-  </si>
-  <si>
     <t xml:space="preserve">Miscomminication with goals for project </t>
   </si>
   <si>
@@ -397,6 +385,48 @@
   </si>
   <si>
     <t xml:space="preserve">If communication isn't done effectively  </t>
+  </si>
+  <si>
+    <t>This risk can arise at any time or iteration of the project.</t>
+  </si>
+  <si>
+    <t>If changes are made to the plan that were not agreed upon.</t>
+  </si>
+  <si>
+    <t>Refering to agreed required tasks to complete the project, using schedueling tools (kanban, gantt) to keep on track.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No current response, no extra tasks. </t>
+  </si>
+  <si>
+    <t>This risk can arise before launching the website.</t>
+  </si>
+  <si>
+    <t>If testing is not done properly.</t>
+  </si>
+  <si>
+    <t>Testing website, links, navigating the website and using User Acceptance Test Result documentation to note these tests.</t>
+  </si>
+  <si>
+    <t>Currently testing website for correct formatting before launch.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>Scope Creep: If extra tasks arise that were not agreed upon at initial project agreement with stakeholders, then will cause the overall completion of the project to require more time and money.</t>
+  </si>
+  <si>
+    <t>Inadequte Testing: If testing is neglected or minimal, e.g. at website launch, then it could affect the launch, delaying the project while errors are fixed and tested.</t>
+  </si>
+  <si>
+    <t>This risk can arise when making changes to the repository.</t>
+  </si>
+  <si>
+    <t>Git Repository Issues: If syncing git repository doesn't sync correctly with other project members, then it will affect the progress and clarity of the project, and clone respositories.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">When </t>
   </si>
 </sst>
 </file>
@@ -405,7 +435,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="mm/dd/yy;@"/>
-    <numFmt numFmtId="165" formatCode="dd/mm/yy;@"/>
+    <numFmt numFmtId="167" formatCode="d/mm/yy;@"/>
   </numFmts>
   <fonts count="21" x14ac:knownFonts="1">
     <font>
@@ -965,9 +995,6 @@
     <xf numFmtId="0" fontId="2" fillId="22" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="16" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
@@ -976,6 +1003,9 @@
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="16" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1836,26 +1866,26 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:IW27"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="3.375" customWidth="1"/>
-    <col min="2" max="2" width="10.875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="10.875" style="5" customWidth="1"/>
+    <col min="1" max="1" width="3.33203125" customWidth="1"/>
+    <col min="2" max="2" width="10.83203125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="10.83203125" style="5" customWidth="1"/>
     <col min="4" max="4" width="13.5" style="1" customWidth="1"/>
     <col min="5" max="5" width="20.5" style="1" customWidth="1"/>
-    <col min="6" max="6" width="12.875" style="5" customWidth="1"/>
-    <col min="7" max="7" width="12.875" style="1" customWidth="1"/>
-    <col min="8" max="8" width="13.875" style="1" customWidth="1"/>
-    <col min="9" max="9" width="20.875" style="1" customWidth="1"/>
-    <col min="10" max="10" width="15.875" style="1" customWidth="1"/>
-    <col min="11" max="11" width="25.875" style="1" customWidth="1"/>
-    <col min="12" max="12" width="15.875" style="1" customWidth="1"/>
-    <col min="13" max="13" width="12.875" style="1" customWidth="1"/>
-    <col min="14" max="14" width="20.875" style="1" customWidth="1"/>
-    <col min="15" max="15" width="3.375" customWidth="1"/>
+    <col min="6" max="6" width="12.83203125" style="5" customWidth="1"/>
+    <col min="7" max="7" width="12.83203125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="13.83203125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="20.83203125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="15.83203125" style="1" customWidth="1"/>
+    <col min="11" max="11" width="25.83203125" style="1" customWidth="1"/>
+    <col min="12" max="12" width="15.83203125" style="1" customWidth="1"/>
+    <col min="13" max="13" width="12.83203125" style="1" customWidth="1"/>
+    <col min="14" max="14" width="20.83203125" style="1" customWidth="1"/>
+    <col min="15" max="15" width="3.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:257" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:257" x14ac:dyDescent="0.35">
       <c r="B1"/>
       <c r="C1"/>
       <c r="D1"/>
@@ -1870,7 +1900,7 @@
       <c r="M1"/>
       <c r="N1"/>
     </row>
-    <row r="2" spans="1:257" s="46" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:257" s="46" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="47"/>
       <c r="B2" s="48" t="s">
         <v>76</v>
@@ -2131,7 +2161,7 @@
       <c r="IV2" s="47"/>
       <c r="IW2" s="47"/>
     </row>
-    <row r="3" spans="1:257" ht="138.94999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:257" ht="139" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C3" s="1"/>
       <c r="F3" s="1"/>
       <c r="K3"/>
@@ -2139,13 +2169,13 @@
       <c r="M3"/>
       <c r="N3"/>
     </row>
-    <row r="4" spans="1:257" ht="78.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:257" ht="79" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B4" s="63"/>
       <c r="C4"/>
-      <c r="D4" s="69" t="s">
+      <c r="D4" s="68" t="s">
         <v>45</v>
       </c>
-      <c r="E4" s="69"/>
+      <c r="E4" s="68"/>
       <c r="F4"/>
       <c r="G4"/>
       <c r="H4" s="62" t="s">
@@ -2158,7 +2188,7 @@
       <c r="M4"/>
       <c r="N4"/>
     </row>
-    <row r="5" spans="1:257" s="4" customFormat="1" ht="54.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:257" s="4" customFormat="1" ht="55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3"/>
       <c r="B5" s="49" t="s">
         <v>0</v>
@@ -2201,7 +2231,7 @@
       </c>
       <c r="O5" s="3"/>
     </row>
-    <row r="6" spans="1:257" ht="108" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:257" ht="100" x14ac:dyDescent="0.35">
       <c r="B6" s="53">
         <v>10001</v>
       </c>
@@ -2241,7 +2271,7 @@
       </c>
       <c r="N6" s="65"/>
     </row>
-    <row r="7" spans="1:257" ht="121.5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:257" ht="100" x14ac:dyDescent="0.35">
       <c r="B7" s="55">
         <v>10002</v>
       </c>
@@ -2281,7 +2311,7 @@
       </c>
       <c r="N7" s="65"/>
     </row>
-    <row r="8" spans="1:257" ht="108" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:257" ht="100" x14ac:dyDescent="0.35">
       <c r="B8" s="55">
         <v>10003</v>
       </c>
@@ -2321,7 +2351,7 @@
       </c>
       <c r="N8" s="65"/>
     </row>
-    <row r="9" spans="1:257" ht="81" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:257" ht="75" x14ac:dyDescent="0.35">
       <c r="B9" s="55">
         <v>10004</v>
       </c>
@@ -2361,7 +2391,7 @@
       </c>
       <c r="N9" s="65"/>
     </row>
-    <row r="10" spans="1:257" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:257" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B10" s="55"/>
       <c r="C10" s="54"/>
       <c r="D10" s="39"/>
@@ -2383,7 +2413,7 @@
       <c r="M10" s="64"/>
       <c r="N10" s="65"/>
     </row>
-    <row r="11" spans="1:257" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:257" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B11" s="55"/>
       <c r="C11" s="54"/>
       <c r="D11" s="39"/>
@@ -2405,7 +2435,7 @@
       <c r="M11" s="64"/>
       <c r="N11" s="65"/>
     </row>
-    <row r="12" spans="1:257" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:257" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B12" s="55"/>
       <c r="C12" s="54"/>
       <c r="D12" s="39"/>
@@ -2427,7 +2457,7 @@
       <c r="M12" s="64"/>
       <c r="N12" s="65"/>
     </row>
-    <row r="13" spans="1:257" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:257" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B13" s="55"/>
       <c r="C13" s="54"/>
       <c r="D13" s="39"/>
@@ -2449,7 +2479,7 @@
       <c r="M13" s="64"/>
       <c r="N13" s="65"/>
     </row>
-    <row r="14" spans="1:257" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:257" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B14" s="55"/>
       <c r="C14" s="54"/>
       <c r="D14" s="39"/>
@@ -2471,7 +2501,7 @@
       <c r="M14" s="64"/>
       <c r="N14" s="65"/>
     </row>
-    <row r="15" spans="1:257" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:257" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B15" s="55"/>
       <c r="C15" s="54"/>
       <c r="D15" s="39"/>
@@ -2493,7 +2523,7 @@
       <c r="M15" s="64"/>
       <c r="N15" s="65"/>
     </row>
-    <row r="16" spans="1:257" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:257" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B16" s="55"/>
       <c r="C16" s="54"/>
       <c r="D16" s="39"/>
@@ -2515,7 +2545,7 @@
       <c r="M16" s="64"/>
       <c r="N16" s="65"/>
     </row>
-    <row r="17" spans="2:14" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:14" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B17" s="55"/>
       <c r="C17" s="54"/>
       <c r="D17" s="39"/>
@@ -2537,7 +2567,7 @@
       <c r="M17" s="64"/>
       <c r="N17" s="65"/>
     </row>
-    <row r="18" spans="2:14" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:14" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B18" s="55"/>
       <c r="C18" s="54"/>
       <c r="D18" s="39"/>
@@ -2559,15 +2589,15 @@
       <c r="M18" s="64"/>
       <c r="N18" s="65"/>
     </row>
-    <row r="19" spans="2:14" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="20" spans="2:14" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="21" spans="2:14" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="22" spans="2:14" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="23" spans="2:14" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="24" spans="2:14" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="25" spans="2:14" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="26" spans="2:14" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="27" spans="2:14" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="19" spans="2:14" ht="18" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="20" spans="2:14" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="21" spans="2:14" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="22" spans="2:14" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="23" spans="2:14" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="24" spans="2:14" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="25" spans="2:14" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="26" spans="2:14" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="27" spans="2:14" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="D4:E4"/>
@@ -2664,24 +2694,26 @@
     <tabColor theme="3" tint="0.79998168889431442"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:IW43"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:IW45"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="3.375" customWidth="1"/>
-    <col min="2" max="2" width="10.875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="10.875" style="5" customWidth="1"/>
+    <col min="1" max="1" width="3.33203125" customWidth="1"/>
+    <col min="2" max="2" width="10.83203125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="10.83203125" style="5" customWidth="1"/>
     <col min="4" max="4" width="13.5" style="1" customWidth="1"/>
-    <col min="5" max="5" width="29.375" style="1" customWidth="1"/>
-    <col min="6" max="6" width="12.875" style="5" customWidth="1"/>
-    <col min="7" max="7" width="12.875" style="1" customWidth="1"/>
-    <col min="8" max="8" width="13.875" style="1" customWidth="1"/>
-    <col min="9" max="12" width="15.875" style="1" customWidth="1"/>
-    <col min="13" max="13" width="12.875" style="1" customWidth="1"/>
-    <col min="14" max="14" width="20.875" style="1" customWidth="1"/>
-    <col min="15" max="15" width="3.375" customWidth="1"/>
+    <col min="5" max="5" width="29.33203125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="12.83203125" style="5" customWidth="1"/>
+    <col min="7" max="7" width="12.83203125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="13.83203125" style="1" customWidth="1"/>
+    <col min="9" max="10" width="15.83203125" style="1" customWidth="1"/>
+    <col min="11" max="11" width="20" style="1" customWidth="1"/>
+    <col min="12" max="12" width="15.83203125" style="1" customWidth="1"/>
+    <col min="13" max="13" width="12.83203125" style="1" customWidth="1"/>
+    <col min="14" max="14" width="20.83203125" style="1" customWidth="1"/>
+    <col min="15" max="15" width="3.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:257" s="46" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:257" s="46" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="47"/>
       <c r="B1" s="48" t="s">
         <v>77</v>
@@ -2942,7 +2974,7 @@
       <c r="IV1" s="47"/>
       <c r="IW1" s="47"/>
     </row>
-    <row r="2" spans="1:257" ht="138.94999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:257" ht="139" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C2" s="1"/>
       <c r="F2" s="1"/>
       <c r="K2"/>
@@ -2950,13 +2982,13 @@
       <c r="M2"/>
       <c r="N2"/>
     </row>
-    <row r="3" spans="1:257" ht="78.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:257" ht="79" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B3" s="63"/>
       <c r="C3"/>
-      <c r="D3" s="69" t="s">
+      <c r="D3" s="68" t="s">
         <v>45</v>
       </c>
-      <c r="E3" s="69"/>
+      <c r="E3" s="68"/>
       <c r="F3"/>
       <c r="G3"/>
       <c r="H3" s="62" t="s">
@@ -2969,7 +3001,7 @@
       <c r="M3"/>
       <c r="N3"/>
     </row>
-    <row r="4" spans="1:257" s="4" customFormat="1" ht="54.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:257" s="4" customFormat="1" ht="55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
       <c r="B4" s="49" t="s">
         <v>0</v>
@@ -3012,16 +3044,16 @@
       </c>
       <c r="O4" s="3"/>
     </row>
-    <row r="5" spans="1:257" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:257" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B5" s="53">
         <v>1</v>
       </c>
-      <c r="C5" s="66">
+      <c r="C5" s="69">
         <v>46154</v>
       </c>
       <c r="D5" s="39"/>
       <c r="E5" s="61" t="s">
-        <v>78</v>
+        <v>112</v>
       </c>
       <c r="F5" s="56">
         <v>3</v>
@@ -3030,126 +3062,128 @@
         <v>16</v>
       </c>
       <c r="H5" s="58">
-        <f t="shared" ref="H5:H13" si="0">F5*G5</f>
+        <f t="shared" ref="H5:H15" si="0">F5*G5</f>
         <v>48</v>
       </c>
       <c r="I5" s="61" t="s">
-        <v>80</v>
+        <v>103</v>
       </c>
       <c r="J5" s="61" t="s">
-        <v>81</v>
-      </c>
-      <c r="K5" s="61"/>
-      <c r="L5" s="61"/>
+        <v>104</v>
+      </c>
+      <c r="K5" s="61" t="s">
+        <v>105</v>
+      </c>
+      <c r="L5" s="61" t="s">
+        <v>106</v>
+      </c>
       <c r="M5" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="N5" s="59"/>
     </row>
-    <row r="6" spans="1:257" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="55"/>
-      <c r="C6" s="54"/>
+    <row r="6" spans="1:257" ht="80" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B6" s="53">
+        <v>2</v>
+      </c>
+      <c r="C6" s="69"/>
       <c r="D6" s="39"/>
       <c r="E6" s="61" t="s">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="F6" s="56">
-        <v>2</v>
-      </c>
-      <c r="G6" s="57"/>
+        <v>3</v>
+      </c>
+      <c r="G6" s="57">
+        <v>16</v>
+      </c>
       <c r="H6" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I6" s="61"/>
-      <c r="J6" s="61"/>
-      <c r="K6" s="61"/>
-      <c r="L6" s="61"/>
+        <v>48</v>
+      </c>
+      <c r="I6" s="61" t="s">
+        <v>107</v>
+      </c>
+      <c r="J6" s="61" t="s">
+        <v>108</v>
+      </c>
+      <c r="K6" s="61" t="s">
+        <v>109</v>
+      </c>
+      <c r="L6" s="61" t="s">
+        <v>110</v>
+      </c>
       <c r="M6" s="6"/>
       <c r="N6" s="59"/>
     </row>
-    <row r="7" spans="1:257" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="55">
+    <row r="7" spans="1:257" ht="80" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B7" s="53">
         <v>3</v>
       </c>
-      <c r="C7" s="54">
-        <v>46155</v>
-      </c>
+      <c r="C7" s="69"/>
       <c r="D7" s="39"/>
       <c r="E7" s="61" t="s">
-        <v>83</v>
+        <v>111</v>
       </c>
       <c r="F7" s="56">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G7" s="57">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="H7" s="58">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="I7" s="61" t="s">
-        <v>84</v>
-      </c>
-      <c r="J7" s="61" t="s">
-        <v>106</v>
-      </c>
-      <c r="K7" s="61" t="s">
-        <v>85</v>
-      </c>
-      <c r="L7" s="61" t="s">
-        <v>86</v>
-      </c>
-      <c r="M7" s="6" t="s">
-        <v>99</v>
-      </c>
+      <c r="I7" s="61"/>
+      <c r="J7" s="61"/>
+      <c r="K7" s="61"/>
+      <c r="L7" s="61"/>
+      <c r="M7" s="6"/>
       <c r="N7" s="59"/>
     </row>
-    <row r="8" spans="1:257" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:257" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B8" s="55">
         <v>4</v>
       </c>
-      <c r="C8" s="54"/>
+      <c r="C8" s="69">
+        <v>46141</v>
+      </c>
       <c r="D8" s="39"/>
       <c r="E8" s="61" t="s">
-        <v>87</v>
+        <v>115</v>
       </c>
       <c r="F8" s="56">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G8" s="57">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="H8" s="58">
         <f t="shared" si="0"/>
-        <v>80</v>
+        <v>8</v>
       </c>
       <c r="I8" s="61" t="s">
-        <v>88</v>
+        <v>114</v>
       </c>
       <c r="J8" s="61" t="s">
-        <v>89</v>
-      </c>
-      <c r="K8" s="67" t="s">
-        <v>91</v>
-      </c>
-      <c r="L8" s="61" t="s">
-        <v>90</v>
-      </c>
-      <c r="M8" s="6" t="s">
-        <v>98</v>
-      </c>
+        <v>116</v>
+      </c>
+      <c r="K8" s="61"/>
+      <c r="L8" s="61"/>
+      <c r="M8" s="6"/>
       <c r="N8" s="59"/>
     </row>
-    <row r="9" spans="1:257" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:257" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B9" s="55">
         <v>5</v>
       </c>
-      <c r="C9" s="54"/>
+      <c r="C9" s="69">
+        <v>46155</v>
+      </c>
       <c r="D9" s="39"/>
       <c r="E9" s="61" t="s">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="F9" s="56">
         <v>2</v>
@@ -3162,97 +3196,133 @@
         <v>16</v>
       </c>
       <c r="I9" s="61" t="s">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="J9" s="61" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="K9" s="61" t="s">
+        <v>81</v>
+      </c>
+      <c r="L9" s="61" t="s">
+        <v>82</v>
+      </c>
+      <c r="M9" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="L9" s="61" t="s">
-        <v>96</v>
-      </c>
-      <c r="M9" s="6" t="s">
-        <v>97</v>
-      </c>
       <c r="N9" s="59"/>
     </row>
-    <row r="10" spans="1:257" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:257" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B10" s="55">
         <v>6</v>
       </c>
-      <c r="C10" s="54"/>
+      <c r="C10" s="69"/>
       <c r="D10" s="39"/>
       <c r="E10" s="61" t="s">
-        <v>105</v>
+        <v>83</v>
       </c>
       <c r="F10" s="56">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G10" s="57">
         <v>16</v>
       </c>
       <c r="H10" s="58">
         <f t="shared" si="0"/>
-        <v>48</v>
+        <v>80</v>
       </c>
       <c r="I10" s="61" t="s">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="J10" s="61" t="s">
-        <v>101</v>
-      </c>
-      <c r="K10" s="68" t="s">
-        <v>102</v>
+        <v>85</v>
+      </c>
+      <c r="K10" s="66" t="s">
+        <v>87</v>
       </c>
       <c r="L10" s="61" t="s">
-        <v>103</v>
+        <v>86</v>
       </c>
       <c r="M10" s="6" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="N10" s="59"/>
     </row>
-    <row r="11" spans="1:257" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="55"/>
-      <c r="C11" s="54"/>
+    <row r="11" spans="1:257" ht="80" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B11" s="55">
+        <v>7</v>
+      </c>
+      <c r="C11" s="69"/>
       <c r="D11" s="39"/>
-      <c r="E11" s="61"/>
-      <c r="F11" s="56"/>
-      <c r="G11" s="57"/>
+      <c r="E11" s="61" t="s">
+        <v>88</v>
+      </c>
+      <c r="F11" s="56">
+        <v>2</v>
+      </c>
+      <c r="G11" s="57">
+        <v>8</v>
+      </c>
       <c r="H11" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I11" s="61"/>
-      <c r="J11" s="61"/>
-      <c r="K11" s="61"/>
-      <c r="L11" s="61"/>
-      <c r="M11" s="6"/>
+        <v>16</v>
+      </c>
+      <c r="I11" s="61" t="s">
+        <v>89</v>
+      </c>
+      <c r="J11" s="61" t="s">
+        <v>90</v>
+      </c>
+      <c r="K11" s="61" t="s">
+        <v>91</v>
+      </c>
+      <c r="L11" s="61" t="s">
+        <v>92</v>
+      </c>
+      <c r="M11" s="6" t="s">
+        <v>93</v>
+      </c>
       <c r="N11" s="59"/>
     </row>
-    <row r="12" spans="1:257" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="55"/>
-      <c r="C12" s="54"/>
+    <row r="12" spans="1:257" ht="80" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B12" s="55">
+        <v>8</v>
+      </c>
+      <c r="C12" s="69"/>
       <c r="D12" s="39"/>
-      <c r="E12" s="61"/>
-      <c r="F12" s="56"/>
-      <c r="G12" s="57"/>
+      <c r="E12" s="61" t="s">
+        <v>101</v>
+      </c>
+      <c r="F12" s="56">
+        <v>3</v>
+      </c>
+      <c r="G12" s="57">
+        <v>16</v>
+      </c>
       <c r="H12" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I12" s="61"/>
-      <c r="J12" s="61"/>
-      <c r="K12" s="61"/>
-      <c r="L12" s="61"/>
-      <c r="M12" s="6"/>
+        <v>48</v>
+      </c>
+      <c r="I12" s="61" t="s">
+        <v>96</v>
+      </c>
+      <c r="J12" s="61" t="s">
+        <v>97</v>
+      </c>
+      <c r="K12" s="67" t="s">
+        <v>98</v>
+      </c>
+      <c r="L12" s="61" t="s">
+        <v>99</v>
+      </c>
+      <c r="M12" s="6" t="s">
+        <v>100</v>
+      </c>
       <c r="N12" s="59"/>
     </row>
-    <row r="13" spans="1:257" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:257" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B13" s="55"/>
-      <c r="C13" s="54"/>
+      <c r="C13" s="69"/>
       <c r="D13" s="39"/>
       <c r="E13" s="61"/>
       <c r="F13" s="56"/>
@@ -3268,15 +3338,15 @@
       <c r="M13" s="6"/>
       <c r="N13" s="59"/>
     </row>
-    <row r="14" spans="1:257" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:257" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B14" s="55"/>
-      <c r="C14" s="54"/>
+      <c r="C14" s="69"/>
       <c r="D14" s="39"/>
       <c r="E14" s="61"/>
       <c r="F14" s="56"/>
       <c r="G14" s="57"/>
       <c r="H14" s="58">
-        <f t="shared" ref="H14:H31" si="1">F14*G14</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="I14" s="61"/>
@@ -3286,15 +3356,15 @@
       <c r="M14" s="6"/>
       <c r="N14" s="59"/>
     </row>
-    <row r="15" spans="1:257" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:257" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B15" s="55"/>
-      <c r="C15" s="54"/>
+      <c r="C15" s="69"/>
       <c r="D15" s="39"/>
       <c r="E15" s="61"/>
       <c r="F15" s="56"/>
       <c r="G15" s="57"/>
       <c r="H15" s="58">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="I15" s="61"/>
@@ -3304,15 +3374,15 @@
       <c r="M15" s="6"/>
       <c r="N15" s="59"/>
     </row>
-    <row r="16" spans="1:257" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:257" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B16" s="55"/>
-      <c r="C16" s="54"/>
+      <c r="C16" s="69"/>
       <c r="D16" s="39"/>
       <c r="E16" s="61"/>
       <c r="F16" s="56"/>
       <c r="G16" s="57"/>
       <c r="H16" s="58">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="H16:H33" si="1">F16*G16</f>
         <v>0</v>
       </c>
       <c r="I16" s="61"/>
@@ -3322,9 +3392,9 @@
       <c r="M16" s="6"/>
       <c r="N16" s="59"/>
     </row>
-    <row r="17" spans="2:14" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:14" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B17" s="55"/>
-      <c r="C17" s="54"/>
+      <c r="C17" s="69"/>
       <c r="D17" s="39"/>
       <c r="E17" s="61"/>
       <c r="F17" s="56"/>
@@ -3340,9 +3410,9 @@
       <c r="M17" s="6"/>
       <c r="N17" s="59"/>
     </row>
-    <row r="18" spans="2:14" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:14" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B18" s="55"/>
-      <c r="C18" s="54"/>
+      <c r="C18" s="69"/>
       <c r="D18" s="39"/>
       <c r="E18" s="61"/>
       <c r="F18" s="56"/>
@@ -3358,9 +3428,9 @@
       <c r="M18" s="6"/>
       <c r="N18" s="59"/>
     </row>
-    <row r="19" spans="2:14" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:14" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B19" s="55"/>
-      <c r="C19" s="54"/>
+      <c r="C19" s="69"/>
       <c r="D19" s="39"/>
       <c r="E19" s="61"/>
       <c r="F19" s="56"/>
@@ -3376,9 +3446,9 @@
       <c r="M19" s="6"/>
       <c r="N19" s="59"/>
     </row>
-    <row r="20" spans="2:14" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:14" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B20" s="55"/>
-      <c r="C20" s="54"/>
+      <c r="C20" s="69"/>
       <c r="D20" s="39"/>
       <c r="E20" s="61"/>
       <c r="F20" s="56"/>
@@ -3394,9 +3464,9 @@
       <c r="M20" s="6"/>
       <c r="N20" s="59"/>
     </row>
-    <row r="21" spans="2:14" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:14" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B21" s="55"/>
-      <c r="C21" s="54"/>
+      <c r="C21" s="69"/>
       <c r="D21" s="39"/>
       <c r="E21" s="61"/>
       <c r="F21" s="56"/>
@@ -3412,9 +3482,9 @@
       <c r="M21" s="6"/>
       <c r="N21" s="59"/>
     </row>
-    <row r="22" spans="2:14" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:14" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B22" s="55"/>
-      <c r="C22" s="54"/>
+      <c r="C22" s="69"/>
       <c r="D22" s="39"/>
       <c r="E22" s="61"/>
       <c r="F22" s="56"/>
@@ -3430,9 +3500,9 @@
       <c r="M22" s="6"/>
       <c r="N22" s="59"/>
     </row>
-    <row r="23" spans="2:14" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:14" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B23" s="55"/>
-      <c r="C23" s="54"/>
+      <c r="C23" s="69"/>
       <c r="D23" s="39"/>
       <c r="E23" s="61"/>
       <c r="F23" s="56"/>
@@ -3448,9 +3518,9 @@
       <c r="M23" s="6"/>
       <c r="N23" s="59"/>
     </row>
-    <row r="24" spans="2:14" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:14" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B24" s="55"/>
-      <c r="C24" s="54"/>
+      <c r="C24" s="69"/>
       <c r="D24" s="39"/>
       <c r="E24" s="61"/>
       <c r="F24" s="56"/>
@@ -3466,9 +3536,9 @@
       <c r="M24" s="6"/>
       <c r="N24" s="59"/>
     </row>
-    <row r="25" spans="2:14" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:14" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B25" s="55"/>
-      <c r="C25" s="54"/>
+      <c r="C25" s="69"/>
       <c r="D25" s="39"/>
       <c r="E25" s="61"/>
       <c r="F25" s="56"/>
@@ -3484,9 +3554,9 @@
       <c r="M25" s="6"/>
       <c r="N25" s="59"/>
     </row>
-    <row r="26" spans="2:14" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:14" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B26" s="55"/>
-      <c r="C26" s="54"/>
+      <c r="C26" s="69"/>
       <c r="D26" s="39"/>
       <c r="E26" s="61"/>
       <c r="F26" s="56"/>
@@ -3502,9 +3572,9 @@
       <c r="M26" s="6"/>
       <c r="N26" s="59"/>
     </row>
-    <row r="27" spans="2:14" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:14" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B27" s="55"/>
-      <c r="C27" s="54"/>
+      <c r="C27" s="69"/>
       <c r="D27" s="39"/>
       <c r="E27" s="61"/>
       <c r="F27" s="56"/>
@@ -3520,9 +3590,9 @@
       <c r="M27" s="6"/>
       <c r="N27" s="59"/>
     </row>
-    <row r="28" spans="2:14" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:14" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B28" s="55"/>
-      <c r="C28" s="54"/>
+      <c r="C28" s="69"/>
       <c r="D28" s="39"/>
       <c r="E28" s="61"/>
       <c r="F28" s="56"/>
@@ -3538,9 +3608,9 @@
       <c r="M28" s="6"/>
       <c r="N28" s="59"/>
     </row>
-    <row r="29" spans="2:14" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:14" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B29" s="55"/>
-      <c r="C29" s="54"/>
+      <c r="C29" s="69"/>
       <c r="D29" s="39"/>
       <c r="E29" s="61"/>
       <c r="F29" s="56"/>
@@ -3556,9 +3626,9 @@
       <c r="M29" s="6"/>
       <c r="N29" s="59"/>
     </row>
-    <row r="30" spans="2:14" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:14" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B30" s="55"/>
-      <c r="C30" s="54"/>
+      <c r="C30" s="69"/>
       <c r="D30" s="39"/>
       <c r="E30" s="61"/>
       <c r="F30" s="56"/>
@@ -3574,9 +3644,9 @@
       <c r="M30" s="6"/>
       <c r="N30" s="59"/>
     </row>
-    <row r="31" spans="2:14" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:14" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B31" s="55"/>
-      <c r="C31" s="54"/>
+      <c r="C31" s="69"/>
       <c r="D31" s="39"/>
       <c r="E31" s="61"/>
       <c r="F31" s="56"/>
@@ -3592,15 +3662,15 @@
       <c r="M31" s="6"/>
       <c r="N31" s="59"/>
     </row>
-    <row r="32" spans="2:14" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:14" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B32" s="55"/>
-      <c r="C32" s="54"/>
+      <c r="C32" s="69"/>
       <c r="D32" s="39"/>
       <c r="E32" s="61"/>
       <c r="F32" s="56"/>
       <c r="G32" s="57"/>
       <c r="H32" s="58">
-        <f t="shared" ref="H32:H34" si="2">F32*G32</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I32" s="61"/>
@@ -3610,15 +3680,15 @@
       <c r="M32" s="6"/>
       <c r="N32" s="59"/>
     </row>
-    <row r="33" spans="2:14" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:14" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B33" s="55"/>
-      <c r="C33" s="54"/>
+      <c r="C33" s="69"/>
       <c r="D33" s="39"/>
       <c r="E33" s="61"/>
       <c r="F33" s="56"/>
       <c r="G33" s="57"/>
       <c r="H33" s="58">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I33" s="61"/>
@@ -3628,15 +3698,15 @@
       <c r="M33" s="6"/>
       <c r="N33" s="59"/>
     </row>
-    <row r="34" spans="2:14" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:14" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B34" s="55"/>
-      <c r="C34" s="54"/>
+      <c r="C34" s="69"/>
       <c r="D34" s="39"/>
       <c r="E34" s="61"/>
       <c r="F34" s="56"/>
       <c r="G34" s="57"/>
       <c r="H34" s="58">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="H34:H36" si="2">F34*G34</f>
         <v>0</v>
       </c>
       <c r="I34" s="61"/>
@@ -3646,20 +3716,56 @@
       <c r="M34" s="6"/>
       <c r="N34" s="59"/>
     </row>
-    <row r="35" spans="2:14" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="36" spans="2:14" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="37" spans="2:14" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="38" spans="2:14" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="39" spans="2:14" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="40" spans="2:14" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="41" spans="2:14" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="42" spans="2:14" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="43" spans="2:14" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="35" spans="2:14" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B35" s="55"/>
+      <c r="C35" s="69"/>
+      <c r="D35" s="39"/>
+      <c r="E35" s="61"/>
+      <c r="F35" s="56"/>
+      <c r="G35" s="57"/>
+      <c r="H35" s="58">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I35" s="61"/>
+      <c r="J35" s="61"/>
+      <c r="K35" s="61"/>
+      <c r="L35" s="61"/>
+      <c r="M35" s="6"/>
+      <c r="N35" s="59"/>
+    </row>
+    <row r="36" spans="2:14" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B36" s="55"/>
+      <c r="C36" s="69"/>
+      <c r="D36" s="39"/>
+      <c r="E36" s="61"/>
+      <c r="F36" s="56"/>
+      <c r="G36" s="57"/>
+      <c r="H36" s="58">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I36" s="61"/>
+      <c r="J36" s="61"/>
+      <c r="K36" s="61"/>
+      <c r="L36" s="61"/>
+      <c r="M36" s="6"/>
+      <c r="N36" s="59"/>
+    </row>
+    <row r="37" spans="2:14" ht="18" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="38" spans="2:14" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="39" spans="2:14" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="40" spans="2:14" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="41" spans="2:14" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="42" spans="2:14" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="43" spans="2:14" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="44" spans="2:14" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="45" spans="2:14" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="D3:E3"/>
   </mergeCells>
-  <conditionalFormatting sqref="F5:F34">
+  <conditionalFormatting sqref="F5:F36">
     <cfRule type="containsText" dxfId="14" priority="1" operator="containsText" text="5">
       <formula>NOT(ISERROR(SEARCH("5",F5)))</formula>
     </cfRule>
@@ -3676,7 +3782,7 @@
       <formula>NOT(ISERROR(SEARCH("1",F5)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G5:G34">
+  <conditionalFormatting sqref="G5:G36">
     <cfRule type="containsText" dxfId="9" priority="11" operator="containsText" text="16">
       <formula>NOT(ISERROR(SEARCH("16",G5)))</formula>
     </cfRule>
@@ -3693,7 +3799,7 @@
       <formula>NOT(ISERROR(SEARCH("1",G5)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H5:H34">
+  <conditionalFormatting sqref="H5:H36">
     <cfRule type="cellIs" dxfId="4" priority="6" operator="between">
       <formula>40</formula>
       <formula>80</formula>
@@ -3725,19 +3831,19 @@
           <x14:formula1>
             <xm:f>'Dropdown Keys – DO NOT DELETE –'!$B$10:$B$14</xm:f>
           </x14:formula1>
-          <xm:sqref>F5:F34</xm:sqref>
+          <xm:sqref>F5:F36</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{F6FA002F-1068-814B-B4FB-03F5370E33EE}">
           <x14:formula1>
             <xm:f>'Dropdown Keys – DO NOT DELETE –'!$C$10:$C$14</xm:f>
           </x14:formula1>
-          <xm:sqref>G5:G34</xm:sqref>
+          <xm:sqref>G5:G36</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{B0984367-0A28-8F4C-8FBF-C2EFA16BE130}">
           <x14:formula1>
             <xm:f>'Dropdown Keys – DO NOT DELETE –'!$B$18:$B$27</xm:f>
           </x14:formula1>
-          <xm:sqref>D5:D34</xm:sqref>
+          <xm:sqref>D5:D36</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -3751,21 +3857,21 @@
     <tabColor theme="2" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:IX27"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="3.375" customWidth="1"/>
-    <col min="2" max="4" width="22.875" customWidth="1"/>
-    <col min="5" max="5" width="3.375" customWidth="1"/>
+    <col min="1" max="1" width="3.33203125" customWidth="1"/>
+    <col min="2" max="4" width="22.83203125" customWidth="1"/>
+    <col min="5" max="5" width="3.33203125" customWidth="1"/>
     <col min="6" max="6" width="4" customWidth="1"/>
-    <col min="7" max="7" width="3.375" customWidth="1"/>
+    <col min="7" max="7" width="3.33203125" customWidth="1"/>
     <col min="13" max="13" width="6.5" customWidth="1"/>
-    <col min="14" max="14" width="19.875" customWidth="1"/>
-    <col min="15" max="15" width="3.375" customWidth="1"/>
-    <col min="16" max="16" width="19.875" customWidth="1"/>
-    <col min="17" max="17" width="3.375" customWidth="1"/>
+    <col min="14" max="14" width="19.83203125" customWidth="1"/>
+    <col min="15" max="15" width="3.33203125" customWidth="1"/>
+    <col min="16" max="16" width="19.83203125" customWidth="1"/>
+    <col min="17" max="17" width="3.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:258" s="46" customFormat="1" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:258" s="46" customFormat="1" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="47"/>
       <c r="B1" s="48" t="s">
         <v>27</v>
@@ -4027,7 +4133,7 @@
       <c r="IW1" s="47"/>
       <c r="IX1" s="47"/>
     </row>
-    <row r="2" spans="1:258" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:258" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B2" s="45" t="s">
         <v>26</v>
       </c>
@@ -4057,7 +4163,7 @@
       <c r="M2" s="43"/>
       <c r="O2" s="42"/>
     </row>
-    <row r="3" spans="1:258" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:258" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B3" s="40" t="s">
         <v>21</v>
       </c>
@@ -4094,7 +4200,7 @@
       <c r="M3" s="2"/>
       <c r="O3" s="19"/>
     </row>
-    <row r="4" spans="1:258" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:258" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B4" s="35" t="s">
         <v>18</v>
       </c>
@@ -4131,7 +4237,7 @@
       <c r="M4" s="2"/>
       <c r="O4" s="19"/>
     </row>
-    <row r="5" spans="1:258" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:258" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B5" s="29" t="s">
         <v>15</v>
       </c>
@@ -4168,7 +4274,7 @@
       <c r="M5" s="2"/>
       <c r="O5" s="19"/>
     </row>
-    <row r="6" spans="1:258" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:258" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B6" s="24" t="s">
         <v>12</v>
       </c>
@@ -4205,7 +4311,7 @@
       <c r="M6" s="2"/>
       <c r="O6" s="19"/>
     </row>
-    <row r="7" spans="1:258" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:258" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B7" s="17" t="s">
         <v>9</v>
       </c>
@@ -4240,7 +4346,7 @@
       </c>
       <c r="O7" s="10"/>
     </row>
-    <row r="8" spans="1:258" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:258" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="G8" s="8"/>
       <c r="H8" s="8"/>
       <c r="I8" s="8"/>
@@ -4248,7 +4354,7 @@
       <c r="K8" s="8"/>
       <c r="L8" s="8"/>
     </row>
-    <row r="9" spans="1:258" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:258" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B9" s="41" t="s">
         <v>23</v>
       </c>
@@ -4256,7 +4362,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="10" spans="1:258" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:258" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B10" s="37">
         <v>1</v>
       </c>
@@ -4264,7 +4370,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:258" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:258" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B11" s="31">
         <v>2</v>
       </c>
@@ -4272,7 +4378,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:258" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:258" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B12" s="26">
         <v>3</v>
       </c>
@@ -4280,7 +4386,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:258" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:258" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B13" s="20">
         <v>4</v>
       </c>
@@ -4288,7 +4394,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="14" spans="1:258" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:258" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B14" s="11">
         <v>5</v>
       </c>
@@ -4296,62 +4402,62 @@
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:258" ht="44.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:258" ht="44.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B16" s="63" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="17" spans="2:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:2" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B17" s="45" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="2:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:2" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B18" s="60" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="19" spans="2:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:2" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B19" s="60" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="20" spans="2:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:2" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B20" s="60" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="21" spans="2:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:2" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B21" s="60" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="22" spans="2:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:2" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B22" s="60" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="23" spans="2:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:2" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B23" s="60" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="24" spans="2:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:2" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B24" s="60" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="25" spans="2:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:2" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B25" s="60" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="26" spans="2:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:2" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B26" s="60" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="27" spans="2:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:2" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B27" s="60" t="s">
         <v>43</v>
       </c>

--- a/Iteration 3/Risk-Register.xlsx
+++ b/Iteration 3/Risk-Register.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://temahau-my.sharepoint.com/personal/sellws2_student_eit_ac_nz/Documents/Documents/ITPM5.240 Agile Projects/Assignments/AgileProjects_Repository/Iteration 3/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="116" documentId="13_ncr:1_{8A2F9314-DDDE-456B-86E7-E230A005C34E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BF9CD29A-52B2-4EBA-8999-6AA8AB4D59CB}"/>
+  <xr:revisionPtr revIDLastSave="151" documentId="13_ncr:1_{8A2F9314-DDDE-456B-86E7-E230A005C34E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4B40BBD0-7BD3-4909-8070-60BB4236E346}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="124">
   <si>
     <t>REF ID</t>
   </si>
@@ -312,9 +312,6 @@
     <t>PROJECT RISK REGISTER TEMPALTE</t>
   </si>
   <si>
-    <t>Project Manager, All Members</t>
-  </si>
-  <si>
     <t xml:space="preserve">Miscomminication with goals for project </t>
   </si>
   <si>
@@ -411,9 +408,6 @@
     <t>Currently testing website for correct formatting before launch.</t>
   </si>
   <si>
-    <t xml:space="preserve"> </t>
-  </si>
-  <si>
     <t>Scope Creep: If extra tasks arise that were not agreed upon at initial project agreement with stakeholders, then will cause the overall completion of the project to require more time and money.</t>
   </si>
   <si>
@@ -426,7 +420,34 @@
     <t>Git Repository Issues: If syncing git repository doesn't sync correctly with other project members, then it will affect the progress and clarity of the project, and clone respositories.</t>
   </si>
   <si>
-    <t xml:space="preserve">When </t>
+    <t>If changes have been made to repository and doesn't sync properly.</t>
+  </si>
+  <si>
+    <t>Checking main remote repository on GitHub, if it doesn't match, re-clone repository to local directory.</t>
+  </si>
+  <si>
+    <t>No issues with syncing of repository currently.</t>
+  </si>
+  <si>
+    <t>Project Manager, Project Members</t>
+  </si>
+  <si>
+    <t>Under Performance: If a member/stakeholder contributing to the project is unable to deliver their task on time or to standard, then tasks are delayed and cost of project increases.</t>
+  </si>
+  <si>
+    <t>This risk can arise at any time during the project.</t>
+  </si>
+  <si>
+    <t>Deliverables are incomplete/poor standard,</t>
+  </si>
+  <si>
+    <t>Weekly Meetings to make sure everyone is on track, using Kanban to monitor progress and task assignments.</t>
+  </si>
+  <si>
+    <t>No current response.</t>
+  </si>
+  <si>
+    <t>Issue last fixed by cloning GitHub repository again. 29/04/26</t>
   </si>
 </sst>
 </file>
@@ -3053,7 +3074,7 @@
       </c>
       <c r="D5" s="39"/>
       <c r="E5" s="61" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="F5" s="56">
         <v>3</v>
@@ -3066,19 +3087,19 @@
         <v>48</v>
       </c>
       <c r="I5" s="61" t="s">
+        <v>102</v>
+      </c>
+      <c r="J5" s="61" t="s">
         <v>103</v>
       </c>
-      <c r="J5" s="61" t="s">
+      <c r="K5" s="61" t="s">
         <v>104</v>
       </c>
-      <c r="K5" s="61" t="s">
+      <c r="L5" s="61" t="s">
         <v>105</v>
       </c>
-      <c r="L5" s="61" t="s">
-        <v>106</v>
-      </c>
       <c r="M5" s="6" t="s">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="N5" s="59"/>
     </row>
@@ -3086,10 +3107,12 @@
       <c r="B6" s="53">
         <v>2</v>
       </c>
-      <c r="C6" s="69"/>
+      <c r="C6" s="69">
+        <v>46155</v>
+      </c>
       <c r="D6" s="39"/>
       <c r="E6" s="61" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="F6" s="56">
         <v>3</v>
@@ -3102,44 +3125,58 @@
         <v>48</v>
       </c>
       <c r="I6" s="61" t="s">
+        <v>106</v>
+      </c>
+      <c r="J6" s="61" t="s">
         <v>107</v>
       </c>
-      <c r="J6" s="61" t="s">
+      <c r="K6" s="61" t="s">
         <v>108</v>
       </c>
-      <c r="K6" s="61" t="s">
+      <c r="L6" s="61" t="s">
         <v>109</v>
       </c>
-      <c r="L6" s="61" t="s">
-        <v>110</v>
-      </c>
-      <c r="M6" s="6"/>
+      <c r="M6" s="6" t="s">
+        <v>92</v>
+      </c>
       <c r="N6" s="59"/>
     </row>
     <row r="7" spans="1:257" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B7" s="53">
         <v>3</v>
       </c>
-      <c r="C7" s="69"/>
+      <c r="C7" s="69">
+        <v>46155</v>
+      </c>
       <c r="D7" s="39"/>
       <c r="E7" s="61" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="F7" s="56">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G7" s="57">
         <v>16</v>
       </c>
       <c r="H7" s="58">
         <f t="shared" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="I7" s="61"/>
-      <c r="J7" s="61"/>
-      <c r="K7" s="61"/>
-      <c r="L7" s="61"/>
-      <c r="M7" s="6"/>
+        <v>32</v>
+      </c>
+      <c r="I7" s="61" t="s">
+        <v>119</v>
+      </c>
+      <c r="J7" s="61" t="s">
+        <v>120</v>
+      </c>
+      <c r="K7" s="61" t="s">
+        <v>121</v>
+      </c>
+      <c r="L7" s="61" t="s">
+        <v>122</v>
+      </c>
+      <c r="M7" s="6" t="s">
+        <v>117</v>
+      </c>
       <c r="N7" s="59"/>
     </row>
     <row r="8" spans="1:257" ht="80" customHeight="1" x14ac:dyDescent="0.35">
@@ -3151,7 +3188,7 @@
       </c>
       <c r="D8" s="39"/>
       <c r="E8" s="61" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="F8" s="56">
         <v>2</v>
@@ -3164,15 +3201,23 @@
         <v>8</v>
       </c>
       <c r="I8" s="61" t="s">
+        <v>112</v>
+      </c>
+      <c r="J8" s="61" t="s">
         <v>114</v>
       </c>
-      <c r="J8" s="61" t="s">
+      <c r="K8" s="61" t="s">
+        <v>115</v>
+      </c>
+      <c r="L8" s="61" t="s">
         <v>116</v>
       </c>
-      <c r="K8" s="61"/>
-      <c r="L8" s="61"/>
-      <c r="M8" s="6"/>
-      <c r="N8" s="59"/>
+      <c r="M8" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="N8" s="59" t="s">
+        <v>123</v>
+      </c>
     </row>
     <row r="9" spans="1:257" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B9" s="55">
@@ -3183,7 +3228,7 @@
       </c>
       <c r="D9" s="39"/>
       <c r="E9" s="61" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F9" s="56">
         <v>2</v>
@@ -3196,19 +3241,19 @@
         <v>16</v>
       </c>
       <c r="I9" s="61" t="s">
+        <v>79</v>
+      </c>
+      <c r="J9" s="61" t="s">
+        <v>101</v>
+      </c>
+      <c r="K9" s="61" t="s">
         <v>80</v>
       </c>
-      <c r="J9" s="61" t="s">
-        <v>102</v>
-      </c>
-      <c r="K9" s="61" t="s">
+      <c r="L9" s="61" t="s">
         <v>81</v>
       </c>
-      <c r="L9" s="61" t="s">
-        <v>82</v>
-      </c>
       <c r="M9" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="N9" s="59"/>
     </row>
@@ -3219,7 +3264,7 @@
       <c r="C10" s="69"/>
       <c r="D10" s="39"/>
       <c r="E10" s="61" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F10" s="56">
         <v>5</v>
@@ -3232,19 +3277,19 @@
         <v>80</v>
       </c>
       <c r="I10" s="61" t="s">
+        <v>83</v>
+      </c>
+      <c r="J10" s="61" t="s">
         <v>84</v>
       </c>
-      <c r="J10" s="61" t="s">
+      <c r="K10" s="66" t="s">
+        <v>86</v>
+      </c>
+      <c r="L10" s="61" t="s">
         <v>85</v>
       </c>
-      <c r="K10" s="66" t="s">
-        <v>87</v>
-      </c>
-      <c r="L10" s="61" t="s">
-        <v>86</v>
-      </c>
       <c r="M10" s="6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="N10" s="59"/>
     </row>
@@ -3255,7 +3300,7 @@
       <c r="C11" s="69"/>
       <c r="D11" s="39"/>
       <c r="E11" s="61" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F11" s="56">
         <v>2</v>
@@ -3268,19 +3313,19 @@
         <v>16</v>
       </c>
       <c r="I11" s="61" t="s">
+        <v>88</v>
+      </c>
+      <c r="J11" s="61" t="s">
         <v>89</v>
       </c>
-      <c r="J11" s="61" t="s">
+      <c r="K11" s="61" t="s">
         <v>90</v>
       </c>
-      <c r="K11" s="61" t="s">
+      <c r="L11" s="61" t="s">
         <v>91</v>
       </c>
-      <c r="L11" s="61" t="s">
+      <c r="M11" s="6" t="s">
         <v>92</v>
-      </c>
-      <c r="M11" s="6" t="s">
-        <v>93</v>
       </c>
       <c r="N11" s="59"/>
     </row>
@@ -3291,7 +3336,7 @@
       <c r="C12" s="69"/>
       <c r="D12" s="39"/>
       <c r="E12" s="61" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F12" s="56">
         <v>3</v>
@@ -3304,19 +3349,19 @@
         <v>48</v>
       </c>
       <c r="I12" s="61" t="s">
+        <v>95</v>
+      </c>
+      <c r="J12" s="61" t="s">
         <v>96</v>
       </c>
-      <c r="J12" s="61" t="s">
+      <c r="K12" s="67" t="s">
         <v>97</v>
       </c>
-      <c r="K12" s="67" t="s">
+      <c r="L12" s="61" t="s">
         <v>98</v>
       </c>
-      <c r="L12" s="61" t="s">
+      <c r="M12" s="6" t="s">
         <v>99</v>
-      </c>
-      <c r="M12" s="6" t="s">
-        <v>100</v>
       </c>
       <c r="N12" s="59"/>
     </row>

--- a/Iteration 3/Risk-Register.xlsx
+++ b/Iteration 3/Risk-Register.xlsx
@@ -5,12 +5,12 @@
   <workbookPr autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://temahau-my.sharepoint.com/personal/sellws2_student_eit_ac_nz/Documents/Documents/ITPM5.240 Agile Projects/Assignments/AgileProjects_Repository/Iteration 3/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b444fedf9e291051/Desktop/AgileProjects_Repository/Iteration 3/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="151" documentId="13_ncr:1_{8A2F9314-DDDE-456B-86E7-E230A005C34E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4B40BBD0-7BD3-4909-8070-60BB4236E346}"/>
+  <xr:revisionPtr revIDLastSave="191" documentId="13_ncr:1_{8A2F9314-DDDE-456B-86E7-E230A005C34E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{44FB3796-F048-49BB-8322-EF594F485D81}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Example risk register" sheetId="8" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="142">
   <si>
     <t>REF ID</t>
   </si>
@@ -345,9 +345,6 @@
     <t>difficult development stages/any time</t>
   </si>
   <si>
-    <t>asinging big work loads to developer</t>
-  </si>
-  <si>
     <t>hire a new developer/break up work laods</t>
   </si>
   <si>
@@ -448,6 +445,63 @@
   </si>
   <si>
     <t>Issue last fixed by cloning GitHub repository again. 29/04/26</t>
+  </si>
+  <si>
+    <t>coding system does not sync correctly with website files</t>
+  </si>
+  <si>
+    <t>this risk can happen at any time during the project</t>
+  </si>
+  <si>
+    <t>assigning big work loads to developer</t>
+  </si>
+  <si>
+    <t>the application or git repo was not syncing properly</t>
+  </si>
+  <si>
+    <t>regularly testing, use version control and back up files before updates</t>
+  </si>
+  <si>
+    <t>regularly ensuring files are synced</t>
+  </si>
+  <si>
+    <t>developer</t>
+  </si>
+  <si>
+    <t>project deadlines may not be met due to time management issues</t>
+  </si>
+  <si>
+    <t>this risk can happen close to deadline time</t>
+  </si>
+  <si>
+    <t>work overload issues and time management issues due to many projects in many classes</t>
+  </si>
+  <si>
+    <t>checking that all members are ensuring this class is a priority and completing work before due date</t>
+  </si>
+  <si>
+    <t>regularly communicating and checking work is completed</t>
+  </si>
+  <si>
+    <t>project manager</t>
+  </si>
+  <si>
+    <t>limited experience using these platforms and coding may cause development mistakes</t>
+  </si>
+  <si>
+    <t>this risk can happen any time</t>
+  </si>
+  <si>
+    <t>incorrect actions on website and platforms</t>
+  </si>
+  <si>
+    <t xml:space="preserve">watch video tutorials, check git powerpoint, ask classmates and teacher </t>
+  </si>
+  <si>
+    <t xml:space="preserve">seeking guidance and checking with others before completing actions as to not corrupt </t>
+  </si>
+  <si>
+    <t>internet connection problems may disturb development work</t>
   </si>
 </sst>
 </file>
@@ -456,9 +510,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="mm/dd/yy;@"/>
-    <numFmt numFmtId="167" formatCode="d/mm/yy;@"/>
+    <numFmt numFmtId="165" formatCode="d/mm/yy;@"/>
   </numFmts>
-  <fonts count="21" x14ac:knownFonts="1">
+  <fonts count="22" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -596,6 +650,12 @@
       <color theme="1"/>
       <name val="Century Gothic"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="7.3"/>
+      <color theme="1"/>
+      <name val="Century Gothic"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="23">
@@ -827,7 +887,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1" indent="1"/>
@@ -1022,11 +1082,14 @@
     <xf numFmtId="0" fontId="20" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="165" fontId="2" fillId="16" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="2" fillId="16" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1887,26 +1950,26 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:IW27"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.33203125" customWidth="1"/>
-    <col min="2" max="2" width="10.83203125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="10.83203125" style="5" customWidth="1"/>
+    <col min="1" max="1" width="3.375" customWidth="1"/>
+    <col min="2" max="2" width="10.875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="10.875" style="5" customWidth="1"/>
     <col min="4" max="4" width="13.5" style="1" customWidth="1"/>
     <col min="5" max="5" width="20.5" style="1" customWidth="1"/>
-    <col min="6" max="6" width="12.83203125" style="5" customWidth="1"/>
-    <col min="7" max="7" width="12.83203125" style="1" customWidth="1"/>
-    <col min="8" max="8" width="13.83203125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="20.83203125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="15.83203125" style="1" customWidth="1"/>
-    <col min="11" max="11" width="25.83203125" style="1" customWidth="1"/>
-    <col min="12" max="12" width="15.83203125" style="1" customWidth="1"/>
-    <col min="13" max="13" width="12.83203125" style="1" customWidth="1"/>
-    <col min="14" max="14" width="20.83203125" style="1" customWidth="1"/>
-    <col min="15" max="15" width="3.33203125" customWidth="1"/>
+    <col min="6" max="6" width="12.875" style="5" customWidth="1"/>
+    <col min="7" max="7" width="12.875" style="1" customWidth="1"/>
+    <col min="8" max="8" width="13.875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="20.875" style="1" customWidth="1"/>
+    <col min="10" max="10" width="15.875" style="1" customWidth="1"/>
+    <col min="11" max="11" width="25.875" style="1" customWidth="1"/>
+    <col min="12" max="12" width="15.875" style="1" customWidth="1"/>
+    <col min="13" max="13" width="12.875" style="1" customWidth="1"/>
+    <col min="14" max="14" width="20.875" style="1" customWidth="1"/>
+    <col min="15" max="15" width="3.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:257" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:257" x14ac:dyDescent="0.25">
       <c r="B1"/>
       <c r="C1"/>
       <c r="D1"/>
@@ -1921,7 +1984,7 @@
       <c r="M1"/>
       <c r="N1"/>
     </row>
-    <row r="2" spans="1:257" s="46" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:257" s="46" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="47"/>
       <c r="B2" s="48" t="s">
         <v>76</v>
@@ -2182,7 +2245,7 @@
       <c r="IV2" s="47"/>
       <c r="IW2" s="47"/>
     </row>
-    <row r="3" spans="1:257" ht="139" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:257" ht="138.94999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C3" s="1"/>
       <c r="F3" s="1"/>
       <c r="K3"/>
@@ -2190,13 +2253,13 @@
       <c r="M3"/>
       <c r="N3"/>
     </row>
-    <row r="4" spans="1:257" ht="79" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:257" ht="78.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B4" s="63"/>
       <c r="C4"/>
-      <c r="D4" s="68" t="s">
+      <c r="D4" s="69" t="s">
         <v>45</v>
       </c>
-      <c r="E4" s="68"/>
+      <c r="E4" s="69"/>
       <c r="F4"/>
       <c r="G4"/>
       <c r="H4" s="62" t="s">
@@ -2209,7 +2272,7 @@
       <c r="M4"/>
       <c r="N4"/>
     </row>
-    <row r="5" spans="1:257" s="4" customFormat="1" ht="55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:257" s="4" customFormat="1" ht="54.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="3"/>
       <c r="B5" s="49" t="s">
         <v>0</v>
@@ -2252,7 +2315,7 @@
       </c>
       <c r="O5" s="3"/>
     </row>
-    <row r="6" spans="1:257" ht="100" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:257" ht="108" x14ac:dyDescent="0.25">
       <c r="B6" s="53">
         <v>10001</v>
       </c>
@@ -2292,7 +2355,7 @@
       </c>
       <c r="N6" s="65"/>
     </row>
-    <row r="7" spans="1:257" ht="100" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:257" ht="121.5" x14ac:dyDescent="0.25">
       <c r="B7" s="55">
         <v>10002</v>
       </c>
@@ -2332,7 +2395,7 @@
       </c>
       <c r="N7" s="65"/>
     </row>
-    <row r="8" spans="1:257" ht="100" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:257" ht="108" x14ac:dyDescent="0.25">
       <c r="B8" s="55">
         <v>10003</v>
       </c>
@@ -2372,7 +2435,7 @@
       </c>
       <c r="N8" s="65"/>
     </row>
-    <row r="9" spans="1:257" ht="75" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:257" ht="81" x14ac:dyDescent="0.25">
       <c r="B9" s="55">
         <v>10004</v>
       </c>
@@ -2412,7 +2475,7 @@
       </c>
       <c r="N9" s="65"/>
     </row>
-    <row r="10" spans="1:257" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:257" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="55"/>
       <c r="C10" s="54"/>
       <c r="D10" s="39"/>
@@ -2434,7 +2497,7 @@
       <c r="M10" s="64"/>
       <c r="N10" s="65"/>
     </row>
-    <row r="11" spans="1:257" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:257" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="55"/>
       <c r="C11" s="54"/>
       <c r="D11" s="39"/>
@@ -2456,7 +2519,7 @@
       <c r="M11" s="64"/>
       <c r="N11" s="65"/>
     </row>
-    <row r="12" spans="1:257" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:257" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="55"/>
       <c r="C12" s="54"/>
       <c r="D12" s="39"/>
@@ -2478,7 +2541,7 @@
       <c r="M12" s="64"/>
       <c r="N12" s="65"/>
     </row>
-    <row r="13" spans="1:257" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:257" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="55"/>
       <c r="C13" s="54"/>
       <c r="D13" s="39"/>
@@ -2500,7 +2563,7 @@
       <c r="M13" s="64"/>
       <c r="N13" s="65"/>
     </row>
-    <row r="14" spans="1:257" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:257" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="55"/>
       <c r="C14" s="54"/>
       <c r="D14" s="39"/>
@@ -2522,7 +2585,7 @@
       <c r="M14" s="64"/>
       <c r="N14" s="65"/>
     </row>
-    <row r="15" spans="1:257" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:257" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="55"/>
       <c r="C15" s="54"/>
       <c r="D15" s="39"/>
@@ -2544,7 +2607,7 @@
       <c r="M15" s="64"/>
       <c r="N15" s="65"/>
     </row>
-    <row r="16" spans="1:257" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:257" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="55"/>
       <c r="C16" s="54"/>
       <c r="D16" s="39"/>
@@ -2566,7 +2629,7 @@
       <c r="M16" s="64"/>
       <c r="N16" s="65"/>
     </row>
-    <row r="17" spans="2:14" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:14" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="55"/>
       <c r="C17" s="54"/>
       <c r="D17" s="39"/>
@@ -2588,7 +2651,7 @@
       <c r="M17" s="64"/>
       <c r="N17" s="65"/>
     </row>
-    <row r="18" spans="2:14" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:14" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="55"/>
       <c r="C18" s="54"/>
       <c r="D18" s="39"/>
@@ -2610,15 +2673,15 @@
       <c r="M18" s="64"/>
       <c r="N18" s="65"/>
     </row>
-    <row r="19" spans="2:14" ht="18" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="20" spans="2:14" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="21" spans="2:14" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="22" spans="2:14" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="23" spans="2:14" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="24" spans="2:14" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="25" spans="2:14" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="26" spans="2:14" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="27" spans="2:14" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="19" spans="2:14" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="20" spans="2:14" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="21" spans="2:14" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="22" spans="2:14" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="23" spans="2:14" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="24" spans="2:14" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="25" spans="2:14" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="26" spans="2:14" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="27" spans="2:14" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="D4:E4"/>
@@ -2716,25 +2779,25 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:IW45"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.33203125" customWidth="1"/>
-    <col min="2" max="2" width="10.83203125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="10.83203125" style="5" customWidth="1"/>
+    <col min="1" max="1" width="3.375" customWidth="1"/>
+    <col min="2" max="2" width="10.875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="10.875" style="5" customWidth="1"/>
     <col min="4" max="4" width="13.5" style="1" customWidth="1"/>
-    <col min="5" max="5" width="29.33203125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="12.83203125" style="5" customWidth="1"/>
-    <col min="7" max="7" width="12.83203125" style="1" customWidth="1"/>
-    <col min="8" max="8" width="13.83203125" style="1" customWidth="1"/>
-    <col min="9" max="10" width="15.83203125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="29.375" style="1" customWidth="1"/>
+    <col min="6" max="6" width="12.875" style="5" customWidth="1"/>
+    <col min="7" max="7" width="12.875" style="1" customWidth="1"/>
+    <col min="8" max="8" width="13.875" style="1" customWidth="1"/>
+    <col min="9" max="10" width="15.875" style="1" customWidth="1"/>
     <col min="11" max="11" width="20" style="1" customWidth="1"/>
-    <col min="12" max="12" width="15.83203125" style="1" customWidth="1"/>
-    <col min="13" max="13" width="12.83203125" style="1" customWidth="1"/>
-    <col min="14" max="14" width="20.83203125" style="1" customWidth="1"/>
-    <col min="15" max="15" width="3.33203125" customWidth="1"/>
+    <col min="12" max="12" width="15.875" style="1" customWidth="1"/>
+    <col min="13" max="13" width="12.875" style="1" customWidth="1"/>
+    <col min="14" max="14" width="20.875" style="1" customWidth="1"/>
+    <col min="15" max="15" width="3.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:257" s="46" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:257" s="46" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="47"/>
       <c r="B1" s="48" t="s">
         <v>77</v>
@@ -2995,7 +3058,7 @@
       <c r="IV1" s="47"/>
       <c r="IW1" s="47"/>
     </row>
-    <row r="2" spans="1:257" ht="139" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:257" ht="138.94999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C2" s="1"/>
       <c r="F2" s="1"/>
       <c r="K2"/>
@@ -3003,13 +3066,13 @@
       <c r="M2"/>
       <c r="N2"/>
     </row>
-    <row r="3" spans="1:257" ht="79" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:257" ht="78.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="63"/>
       <c r="C3"/>
-      <c r="D3" s="68" t="s">
+      <c r="D3" s="69" t="s">
         <v>45</v>
       </c>
-      <c r="E3" s="68"/>
+      <c r="E3" s="69"/>
       <c r="F3"/>
       <c r="G3"/>
       <c r="H3" s="62" t="s">
@@ -3022,7 +3085,7 @@
       <c r="M3"/>
       <c r="N3"/>
     </row>
-    <row r="4" spans="1:257" s="4" customFormat="1" ht="55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:257" s="4" customFormat="1" ht="54.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="3"/>
       <c r="B4" s="49" t="s">
         <v>0</v>
@@ -3065,16 +3128,16 @@
       </c>
       <c r="O4" s="3"/>
     </row>
-    <row r="5" spans="1:257" ht="80" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:257" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="53">
         <v>1</v>
       </c>
-      <c r="C5" s="69">
+      <c r="C5" s="68">
         <v>46154</v>
       </c>
       <c r="D5" s="39"/>
       <c r="E5" s="61" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F5" s="56">
         <v>3</v>
@@ -3087,32 +3150,32 @@
         <v>48</v>
       </c>
       <c r="I5" s="61" t="s">
+        <v>101</v>
+      </c>
+      <c r="J5" s="61" t="s">
         <v>102</v>
       </c>
-      <c r="J5" s="61" t="s">
+      <c r="K5" s="61" t="s">
         <v>103</v>
       </c>
-      <c r="K5" s="61" t="s">
+      <c r="L5" s="61" t="s">
         <v>104</v>
       </c>
-      <c r="L5" s="61" t="s">
-        <v>105</v>
-      </c>
       <c r="M5" s="6" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="N5" s="59"/>
     </row>
-    <row r="6" spans="1:257" ht="80" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:257" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="53">
         <v>2</v>
       </c>
-      <c r="C6" s="69">
+      <c r="C6" s="68">
         <v>46155</v>
       </c>
       <c r="D6" s="39"/>
       <c r="E6" s="61" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F6" s="56">
         <v>3</v>
@@ -3125,32 +3188,32 @@
         <v>48</v>
       </c>
       <c r="I6" s="61" t="s">
+        <v>105</v>
+      </c>
+      <c r="J6" s="61" t="s">
         <v>106</v>
       </c>
-      <c r="J6" s="61" t="s">
+      <c r="K6" s="61" t="s">
         <v>107</v>
       </c>
-      <c r="K6" s="61" t="s">
+      <c r="L6" s="61" t="s">
         <v>108</v>
       </c>
-      <c r="L6" s="61" t="s">
-        <v>109</v>
-      </c>
       <c r="M6" s="6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="N6" s="59"/>
     </row>
-    <row r="7" spans="1:257" ht="80" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:257" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="53">
         <v>3</v>
       </c>
-      <c r="C7" s="69">
+      <c r="C7" s="68">
         <v>46155</v>
       </c>
       <c r="D7" s="39"/>
       <c r="E7" s="61" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F7" s="56">
         <v>2</v>
@@ -3163,32 +3226,32 @@
         <v>32</v>
       </c>
       <c r="I7" s="61" t="s">
+        <v>118</v>
+      </c>
+      <c r="J7" s="61" t="s">
         <v>119</v>
       </c>
-      <c r="J7" s="61" t="s">
+      <c r="K7" s="61" t="s">
         <v>120</v>
       </c>
-      <c r="K7" s="61" t="s">
+      <c r="L7" s="61" t="s">
         <v>121</v>
       </c>
-      <c r="L7" s="61" t="s">
-        <v>122</v>
-      </c>
       <c r="M7" s="6" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="N7" s="59"/>
     </row>
-    <row r="8" spans="1:257" ht="80" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:257" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="55">
         <v>4</v>
       </c>
-      <c r="C8" s="69">
+      <c r="C8" s="68">
         <v>46141</v>
       </c>
       <c r="D8" s="39"/>
       <c r="E8" s="61" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F8" s="56">
         <v>2</v>
@@ -3201,29 +3264,29 @@
         <v>8</v>
       </c>
       <c r="I8" s="61" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="J8" s="61" t="s">
+        <v>113</v>
+      </c>
+      <c r="K8" s="61" t="s">
         <v>114</v>
       </c>
-      <c r="K8" s="61" t="s">
+      <c r="L8" s="61" t="s">
         <v>115</v>
       </c>
-      <c r="L8" s="61" t="s">
+      <c r="M8" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="M8" s="6" t="s">
-        <v>117</v>
-      </c>
       <c r="N8" s="59" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="9" spans="1:257" ht="80" customHeight="1" x14ac:dyDescent="0.35">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="9" spans="1:257" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="55">
         <v>5</v>
       </c>
-      <c r="C9" s="69">
+      <c r="C9" s="68">
         <v>46155</v>
       </c>
       <c r="D9" s="39"/>
@@ -3244,7 +3307,7 @@
         <v>79</v>
       </c>
       <c r="J9" s="61" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="K9" s="61" t="s">
         <v>80</v>
@@ -3253,15 +3316,15 @@
         <v>81</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="N9" s="59"/>
     </row>
-    <row r="10" spans="1:257" ht="80" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:257" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="55">
         <v>6</v>
       </c>
-      <c r="C10" s="69"/>
+      <c r="C10" s="68"/>
       <c r="D10" s="39"/>
       <c r="E10" s="61" t="s">
         <v>82</v>
@@ -3289,15 +3352,15 @@
         <v>85</v>
       </c>
       <c r="M10" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="N10" s="59"/>
     </row>
-    <row r="11" spans="1:257" ht="80" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:257" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="55">
         <v>7</v>
       </c>
-      <c r="C11" s="69"/>
+      <c r="C11" s="68"/>
       <c r="D11" s="39"/>
       <c r="E11" s="61" t="s">
         <v>87</v>
@@ -3316,27 +3379,27 @@
         <v>88</v>
       </c>
       <c r="J11" s="61" t="s">
+        <v>125</v>
+      </c>
+      <c r="K11" s="61" t="s">
         <v>89</v>
       </c>
-      <c r="K11" s="61" t="s">
+      <c r="L11" s="61" t="s">
         <v>90</v>
       </c>
-      <c r="L11" s="61" t="s">
+      <c r="M11" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="M11" s="6" t="s">
-        <v>92</v>
-      </c>
       <c r="N11" s="59"/>
     </row>
-    <row r="12" spans="1:257" ht="80" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:257" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="55">
         <v>8</v>
       </c>
-      <c r="C12" s="69"/>
+      <c r="C12" s="68"/>
       <c r="D12" s="39"/>
       <c r="E12" s="61" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F12" s="56">
         <v>3</v>
@@ -3349,97 +3412,169 @@
         <v>48</v>
       </c>
       <c r="I12" s="61" t="s">
+        <v>94</v>
+      </c>
+      <c r="J12" s="61" t="s">
         <v>95</v>
       </c>
-      <c r="J12" s="61" t="s">
+      <c r="K12" s="67" t="s">
         <v>96</v>
       </c>
-      <c r="K12" s="67" t="s">
+      <c r="L12" s="61" t="s">
         <v>97</v>
       </c>
-      <c r="L12" s="61" t="s">
+      <c r="M12" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="M12" s="6" t="s">
-        <v>99</v>
-      </c>
       <c r="N12" s="59"/>
     </row>
-    <row r="13" spans="1:257" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B13" s="55"/>
-      <c r="C13" s="69"/>
+    <row r="13" spans="1:257" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="55">
+        <v>9</v>
+      </c>
+      <c r="C13" s="68">
+        <v>46148</v>
+      </c>
       <c r="D13" s="39"/>
-      <c r="E13" s="61"/>
-      <c r="F13" s="56"/>
-      <c r="G13" s="57"/>
+      <c r="E13" s="61" t="s">
+        <v>123</v>
+      </c>
+      <c r="F13" s="56">
+        <v>3</v>
+      </c>
+      <c r="G13" s="57">
+        <v>16</v>
+      </c>
       <c r="H13" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I13" s="61"/>
-      <c r="J13" s="61"/>
-      <c r="K13" s="61"/>
-      <c r="L13" s="61"/>
-      <c r="M13" s="6"/>
+        <v>48</v>
+      </c>
+      <c r="I13" s="61" t="s">
+        <v>124</v>
+      </c>
+      <c r="J13" s="61" t="s">
+        <v>126</v>
+      </c>
+      <c r="K13" s="61" t="s">
+        <v>127</v>
+      </c>
+      <c r="L13" s="61" t="s">
+        <v>128</v>
+      </c>
+      <c r="M13" s="6" t="s">
+        <v>129</v>
+      </c>
       <c r="N13" s="59"/>
     </row>
-    <row r="14" spans="1:257" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="55"/>
-      <c r="C14" s="69"/>
+    <row r="14" spans="1:257" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="55">
+        <v>10</v>
+      </c>
+      <c r="C14" s="68">
+        <v>46161</v>
+      </c>
       <c r="D14" s="39"/>
-      <c r="E14" s="61"/>
-      <c r="F14" s="56"/>
-      <c r="G14" s="57"/>
+      <c r="E14" s="61" t="s">
+        <v>130</v>
+      </c>
+      <c r="F14" s="56">
+        <v>3</v>
+      </c>
+      <c r="G14" s="57">
+        <v>8</v>
+      </c>
       <c r="H14" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I14" s="61"/>
-      <c r="J14" s="61"/>
-      <c r="K14" s="61"/>
-      <c r="L14" s="61"/>
-      <c r="M14" s="6"/>
+        <v>24</v>
+      </c>
+      <c r="I14" s="61" t="s">
+        <v>131</v>
+      </c>
+      <c r="J14" s="70" t="s">
+        <v>132</v>
+      </c>
+      <c r="K14" s="61" t="s">
+        <v>133</v>
+      </c>
+      <c r="L14" s="61" t="s">
+        <v>134</v>
+      </c>
+      <c r="M14" s="6" t="s">
+        <v>135</v>
+      </c>
       <c r="N14" s="59"/>
     </row>
-    <row r="15" spans="1:257" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B15" s="55"/>
-      <c r="C15" s="69"/>
+    <row r="15" spans="1:257" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="55">
+        <v>11</v>
+      </c>
+      <c r="C15" s="68">
+        <v>46161</v>
+      </c>
       <c r="D15" s="39"/>
-      <c r="E15" s="61"/>
-      <c r="F15" s="56"/>
-      <c r="G15" s="57"/>
+      <c r="E15" s="61" t="s">
+        <v>136</v>
+      </c>
+      <c r="F15" s="56">
+        <v>5</v>
+      </c>
+      <c r="G15" s="57">
+        <v>16</v>
+      </c>
       <c r="H15" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I15" s="61"/>
-      <c r="J15" s="61"/>
-      <c r="K15" s="61"/>
-      <c r="L15" s="61"/>
-      <c r="M15" s="6"/>
+        <v>80</v>
+      </c>
+      <c r="I15" s="61" t="s">
+        <v>137</v>
+      </c>
+      <c r="J15" s="61" t="s">
+        <v>138</v>
+      </c>
+      <c r="K15" s="61" t="s">
+        <v>139</v>
+      </c>
+      <c r="L15" s="61" t="s">
+        <v>140</v>
+      </c>
+      <c r="M15" s="6" t="s">
+        <v>129</v>
+      </c>
       <c r="N15" s="59"/>
     </row>
-    <row r="16" spans="1:257" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B16" s="55"/>
-      <c r="C16" s="69"/>
+    <row r="16" spans="1:257" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="55">
+        <v>12</v>
+      </c>
+      <c r="C16" s="68">
+        <v>46161</v>
+      </c>
       <c r="D16" s="39"/>
-      <c r="E16" s="61"/>
-      <c r="F16" s="56"/>
-      <c r="G16" s="57"/>
+      <c r="E16" s="61" t="s">
+        <v>141</v>
+      </c>
+      <c r="F16" s="56">
+        <v>2</v>
+      </c>
+      <c r="G16" s="57">
+        <v>4</v>
+      </c>
       <c r="H16" s="58">
         <f t="shared" ref="H16:H33" si="1">F16*G16</f>
-        <v>0</v>
-      </c>
-      <c r="I16" s="61"/>
+        <v>8</v>
+      </c>
+      <c r="I16" s="61" t="s">
+        <v>124</v>
+      </c>
       <c r="J16" s="61"/>
       <c r="K16" s="61"/>
       <c r="L16" s="61"/>
       <c r="M16" s="6"/>
       <c r="N16" s="59"/>
     </row>
-    <row r="17" spans="2:14" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:14" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="55"/>
-      <c r="C17" s="69"/>
+      <c r="C17" s="68"/>
       <c r="D17" s="39"/>
       <c r="E17" s="61"/>
       <c r="F17" s="56"/>
@@ -3455,9 +3590,9 @@
       <c r="M17" s="6"/>
       <c r="N17" s="59"/>
     </row>
-    <row r="18" spans="2:14" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:14" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="55"/>
-      <c r="C18" s="69"/>
+      <c r="C18" s="68"/>
       <c r="D18" s="39"/>
       <c r="E18" s="61"/>
       <c r="F18" s="56"/>
@@ -3473,9 +3608,9 @@
       <c r="M18" s="6"/>
       <c r="N18" s="59"/>
     </row>
-    <row r="19" spans="2:14" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:14" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" s="55"/>
-      <c r="C19" s="69"/>
+      <c r="C19" s="68"/>
       <c r="D19" s="39"/>
       <c r="E19" s="61"/>
       <c r="F19" s="56"/>
@@ -3491,9 +3626,9 @@
       <c r="M19" s="6"/>
       <c r="N19" s="59"/>
     </row>
-    <row r="20" spans="2:14" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:14" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="55"/>
-      <c r="C20" s="69"/>
+      <c r="C20" s="68"/>
       <c r="D20" s="39"/>
       <c r="E20" s="61"/>
       <c r="F20" s="56"/>
@@ -3509,9 +3644,9 @@
       <c r="M20" s="6"/>
       <c r="N20" s="59"/>
     </row>
-    <row r="21" spans="2:14" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:14" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B21" s="55"/>
-      <c r="C21" s="69"/>
+      <c r="C21" s="68"/>
       <c r="D21" s="39"/>
       <c r="E21" s="61"/>
       <c r="F21" s="56"/>
@@ -3527,9 +3662,9 @@
       <c r="M21" s="6"/>
       <c r="N21" s="59"/>
     </row>
-    <row r="22" spans="2:14" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:14" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="55"/>
-      <c r="C22" s="69"/>
+      <c r="C22" s="68"/>
       <c r="D22" s="39"/>
       <c r="E22" s="61"/>
       <c r="F22" s="56"/>
@@ -3545,9 +3680,9 @@
       <c r="M22" s="6"/>
       <c r="N22" s="59"/>
     </row>
-    <row r="23" spans="2:14" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:14" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B23" s="55"/>
-      <c r="C23" s="69"/>
+      <c r="C23" s="68"/>
       <c r="D23" s="39"/>
       <c r="E23" s="61"/>
       <c r="F23" s="56"/>
@@ -3563,9 +3698,9 @@
       <c r="M23" s="6"/>
       <c r="N23" s="59"/>
     </row>
-    <row r="24" spans="2:14" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:14" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24" s="55"/>
-      <c r="C24" s="69"/>
+      <c r="C24" s="68"/>
       <c r="D24" s="39"/>
       <c r="E24" s="61"/>
       <c r="F24" s="56"/>
@@ -3581,9 +3716,9 @@
       <c r="M24" s="6"/>
       <c r="N24" s="59"/>
     </row>
-    <row r="25" spans="2:14" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:14" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B25" s="55"/>
-      <c r="C25" s="69"/>
+      <c r="C25" s="68"/>
       <c r="D25" s="39"/>
       <c r="E25" s="61"/>
       <c r="F25" s="56"/>
@@ -3599,9 +3734,9 @@
       <c r="M25" s="6"/>
       <c r="N25" s="59"/>
     </row>
-    <row r="26" spans="2:14" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:14" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="55"/>
-      <c r="C26" s="69"/>
+      <c r="C26" s="68"/>
       <c r="D26" s="39"/>
       <c r="E26" s="61"/>
       <c r="F26" s="56"/>
@@ -3617,9 +3752,9 @@
       <c r="M26" s="6"/>
       <c r="N26" s="59"/>
     </row>
-    <row r="27" spans="2:14" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:14" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B27" s="55"/>
-      <c r="C27" s="69"/>
+      <c r="C27" s="68"/>
       <c r="D27" s="39"/>
       <c r="E27" s="61"/>
       <c r="F27" s="56"/>
@@ -3635,9 +3770,9 @@
       <c r="M27" s="6"/>
       <c r="N27" s="59"/>
     </row>
-    <row r="28" spans="2:14" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:14" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B28" s="55"/>
-      <c r="C28" s="69"/>
+      <c r="C28" s="68"/>
       <c r="D28" s="39"/>
       <c r="E28" s="61"/>
       <c r="F28" s="56"/>
@@ -3653,9 +3788,9 @@
       <c r="M28" s="6"/>
       <c r="N28" s="59"/>
     </row>
-    <row r="29" spans="2:14" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:14" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B29" s="55"/>
-      <c r="C29" s="69"/>
+      <c r="C29" s="68"/>
       <c r="D29" s="39"/>
       <c r="E29" s="61"/>
       <c r="F29" s="56"/>
@@ -3671,9 +3806,9 @@
       <c r="M29" s="6"/>
       <c r="N29" s="59"/>
     </row>
-    <row r="30" spans="2:14" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:14" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B30" s="55"/>
-      <c r="C30" s="69"/>
+      <c r="C30" s="68"/>
       <c r="D30" s="39"/>
       <c r="E30" s="61"/>
       <c r="F30" s="56"/>
@@ -3689,9 +3824,9 @@
       <c r="M30" s="6"/>
       <c r="N30" s="59"/>
     </row>
-    <row r="31" spans="2:14" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:14" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B31" s="55"/>
-      <c r="C31" s="69"/>
+      <c r="C31" s="68"/>
       <c r="D31" s="39"/>
       <c r="E31" s="61"/>
       <c r="F31" s="56"/>
@@ -3707,9 +3842,9 @@
       <c r="M31" s="6"/>
       <c r="N31" s="59"/>
     </row>
-    <row r="32" spans="2:14" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:14" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B32" s="55"/>
-      <c r="C32" s="69"/>
+      <c r="C32" s="68"/>
       <c r="D32" s="39"/>
       <c r="E32" s="61"/>
       <c r="F32" s="56"/>
@@ -3725,9 +3860,9 @@
       <c r="M32" s="6"/>
       <c r="N32" s="59"/>
     </row>
-    <row r="33" spans="2:14" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:14" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B33" s="55"/>
-      <c r="C33" s="69"/>
+      <c r="C33" s="68"/>
       <c r="D33" s="39"/>
       <c r="E33" s="61"/>
       <c r="F33" s="56"/>
@@ -3743,9 +3878,9 @@
       <c r="M33" s="6"/>
       <c r="N33" s="59"/>
     </row>
-    <row r="34" spans="2:14" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:14" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B34" s="55"/>
-      <c r="C34" s="69"/>
+      <c r="C34" s="68"/>
       <c r="D34" s="39"/>
       <c r="E34" s="61"/>
       <c r="F34" s="56"/>
@@ -3761,9 +3896,9 @@
       <c r="M34" s="6"/>
       <c r="N34" s="59"/>
     </row>
-    <row r="35" spans="2:14" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:14" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B35" s="55"/>
-      <c r="C35" s="69"/>
+      <c r="C35" s="68"/>
       <c r="D35" s="39"/>
       <c r="E35" s="61"/>
       <c r="F35" s="56"/>
@@ -3779,9 +3914,9 @@
       <c r="M35" s="6"/>
       <c r="N35" s="59"/>
     </row>
-    <row r="36" spans="2:14" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:14" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B36" s="55"/>
-      <c r="C36" s="69"/>
+      <c r="C36" s="68"/>
       <c r="D36" s="39"/>
       <c r="E36" s="61"/>
       <c r="F36" s="56"/>
@@ -3797,15 +3932,15 @@
       <c r="M36" s="6"/>
       <c r="N36" s="59"/>
     </row>
-    <row r="37" spans="2:14" ht="18" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="38" spans="2:14" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="39" spans="2:14" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="40" spans="2:14" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="41" spans="2:14" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="42" spans="2:14" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="43" spans="2:14" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="44" spans="2:14" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="45" spans="2:14" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="37" spans="2:14" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="38" spans="2:14" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="39" spans="2:14" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="40" spans="2:14" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="41" spans="2:14" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="42" spans="2:14" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="43" spans="2:14" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="44" spans="2:14" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="45" spans="2:14" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="D3:E3"/>
@@ -3902,21 +4037,21 @@
     <tabColor theme="2" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:IX27"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.33203125" customWidth="1"/>
-    <col min="2" max="4" width="22.83203125" customWidth="1"/>
-    <col min="5" max="5" width="3.33203125" customWidth="1"/>
+    <col min="1" max="1" width="3.375" customWidth="1"/>
+    <col min="2" max="4" width="22.875" customWidth="1"/>
+    <col min="5" max="5" width="3.375" customWidth="1"/>
     <col min="6" max="6" width="4" customWidth="1"/>
-    <col min="7" max="7" width="3.33203125" customWidth="1"/>
+    <col min="7" max="7" width="3.375" customWidth="1"/>
     <col min="13" max="13" width="6.5" customWidth="1"/>
-    <col min="14" max="14" width="19.83203125" customWidth="1"/>
-    <col min="15" max="15" width="3.33203125" customWidth="1"/>
-    <col min="16" max="16" width="19.83203125" customWidth="1"/>
-    <col min="17" max="17" width="3.33203125" customWidth="1"/>
+    <col min="14" max="14" width="19.875" customWidth="1"/>
+    <col min="15" max="15" width="3.375" customWidth="1"/>
+    <col min="16" max="16" width="19.875" customWidth="1"/>
+    <col min="17" max="17" width="3.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:258" s="46" customFormat="1" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:258" s="46" customFormat="1" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="47"/>
       <c r="B1" s="48" t="s">
         <v>27</v>
@@ -4178,7 +4313,7 @@
       <c r="IW1" s="47"/>
       <c r="IX1" s="47"/>
     </row>
-    <row r="2" spans="1:258" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:258" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="45" t="s">
         <v>26</v>
       </c>
@@ -4208,7 +4343,7 @@
       <c r="M2" s="43"/>
       <c r="O2" s="42"/>
     </row>
-    <row r="3" spans="1:258" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:258" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="40" t="s">
         <v>21</v>
       </c>
@@ -4245,7 +4380,7 @@
       <c r="M3" s="2"/>
       <c r="O3" s="19"/>
     </row>
-    <row r="4" spans="1:258" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:258" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="35" t="s">
         <v>18</v>
       </c>
@@ -4282,7 +4417,7 @@
       <c r="M4" s="2"/>
       <c r="O4" s="19"/>
     </row>
-    <row r="5" spans="1:258" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:258" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="29" t="s">
         <v>15</v>
       </c>
@@ -4319,7 +4454,7 @@
       <c r="M5" s="2"/>
       <c r="O5" s="19"/>
     </row>
-    <row r="6" spans="1:258" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:258" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="24" t="s">
         <v>12</v>
       </c>
@@ -4356,7 +4491,7 @@
       <c r="M6" s="2"/>
       <c r="O6" s="19"/>
     </row>
-    <row r="7" spans="1:258" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:258" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="17" t="s">
         <v>9</v>
       </c>
@@ -4391,7 +4526,7 @@
       </c>
       <c r="O7" s="10"/>
     </row>
-    <row r="8" spans="1:258" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:258" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="G8" s="8"/>
       <c r="H8" s="8"/>
       <c r="I8" s="8"/>
@@ -4399,7 +4534,7 @@
       <c r="K8" s="8"/>
       <c r="L8" s="8"/>
     </row>
-    <row r="9" spans="1:258" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:258" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="41" t="s">
         <v>23</v>
       </c>
@@ -4407,7 +4542,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="10" spans="1:258" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:258" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="37">
         <v>1</v>
       </c>
@@ -4415,7 +4550,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:258" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:258" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="31">
         <v>2</v>
       </c>
@@ -4423,7 +4558,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:258" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:258" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="26">
         <v>3</v>
       </c>
@@ -4431,7 +4566,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:258" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:258" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="20">
         <v>4</v>
       </c>
@@ -4439,7 +4574,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="14" spans="1:258" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:258" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="11">
         <v>5</v>
       </c>
@@ -4447,62 +4582,62 @@
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:258" ht="44.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:258" ht="44.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B16" s="63" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="17" spans="2:2" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="45" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="2:2" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="60" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="19" spans="2:2" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" s="60" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="20" spans="2:2" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="60" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="21" spans="2:2" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B21" s="60" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="22" spans="2:2" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="60" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="23" spans="2:2" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B23" s="60" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="24" spans="2:2" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24" s="60" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="25" spans="2:2" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B25" s="60" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="26" spans="2:2" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="60" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="27" spans="2:2" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B27" s="60" t="s">
         <v>43</v>
       </c>

--- a/Iteration 3/Risk-Register.xlsx
+++ b/Iteration 3/Risk-Register.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b444fedf9e291051/Desktop/AgileProjects_Repository/Iteration 3/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="191" documentId="13_ncr:1_{8A2F9314-DDDE-456B-86E7-E230A005C34E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{44FB3796-F048-49BB-8322-EF594F485D81}"/>
+  <xr:revisionPtr revIDLastSave="195" documentId="13_ncr:1_{8A2F9314-DDDE-456B-86E7-E230A005C34E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C17150BE-4FED-4D5D-BF25-039141873156}"/>
   <bookViews>
     <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="145">
   <si>
     <t>REF ID</t>
   </si>
@@ -502,6 +502,15 @@
   </si>
   <si>
     <t>internet connection problems may disturb development work</t>
+  </si>
+  <si>
+    <t>wifi cuts off/powercut due to bad weather</t>
+  </si>
+  <si>
+    <t>ensure work is saved frequently and keep offline copies of important files</t>
+  </si>
+  <si>
+    <t>no issues as of present</t>
   </si>
 </sst>
 </file>
@@ -3566,10 +3575,18 @@
       <c r="I16" s="61" t="s">
         <v>124</v>
       </c>
-      <c r="J16" s="61"/>
-      <c r="K16" s="61"/>
-      <c r="L16" s="61"/>
-      <c r="M16" s="6"/>
+      <c r="J16" s="61" t="s">
+        <v>142</v>
+      </c>
+      <c r="K16" s="61" t="s">
+        <v>143</v>
+      </c>
+      <c r="L16" s="61" t="s">
+        <v>144</v>
+      </c>
+      <c r="M16" s="6" t="s">
+        <v>129</v>
+      </c>
       <c r="N16" s="59"/>
     </row>
     <row r="17" spans="2:14" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
